--- a/data/hex_xlsx/SRV1V.HE.xlsx
+++ b/data/hex_xlsx/SRV1V.HE.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="493">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -958,6 +958,9 @@
   </si>
   <si>
     <t>Misc other L/T liabilities</t>
+  </si>
+  <si>
+    <t>Interest-bearing liabilities LT</t>
   </si>
   <si>
     <t>Other liabilities</t>
@@ -1620,7 +1623,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1698,6 +1701,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -17914,8 +17920,8 @@
       </c>
     </row>
     <row r="132" ht="15.0" customHeight="1">
-      <c r="A132" s="14" t="s">
-        <v>299</v>
+      <c r="A132" s="26" t="s">
+        <v>313</v>
       </c>
       <c r="B132" s="15">
         <v>413.71</v>
@@ -18035,7 +18041,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B134" s="15">
         <v>108.58</v>
@@ -18112,7 +18118,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B135" s="16"/>
       <c r="C135" s="16">
@@ -18157,7 +18163,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B136" s="16"/>
       <c r="C136" s="17">
@@ -18202,7 +18208,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B137" s="16"/>
       <c r="C137" s="16"/>
@@ -18233,7 +18239,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B138" s="16"/>
       <c r="C138" s="16"/>
@@ -18270,7 +18276,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B139" s="16"/>
       <c r="C139" s="22">
@@ -18352,7 +18358,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B141" s="16"/>
       <c r="C141" s="16">
@@ -18385,7 +18391,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="18" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B142" s="19">
         <v>1962.66</v>
@@ -18462,7 +18468,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B143" s="16"/>
       <c r="C143" s="16"/>
@@ -18497,7 +18503,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="18" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B144" s="19">
         <v>3924.85</v>
@@ -18574,7 +18580,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B145" s="17">
         <v>36.19</v>
@@ -18651,7 +18657,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B146" s="16"/>
       <c r="C146" s="16"/>
@@ -18706,7 +18712,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B147" s="15">
         <v>3586.25</v>
@@ -18777,7 +18783,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B148" s="16"/>
       <c r="C148" s="16"/>
@@ -18828,7 +18834,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B149" s="16"/>
       <c r="C149" s="16">
@@ -18899,7 +18905,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B150" s="15">
         <v>543.43</v>
@@ -18954,7 +18960,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B151" s="21">
         <v>-2205.75</v>
@@ -19031,7 +19037,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B152" s="16"/>
       <c r="C152" s="16"/>
@@ -19066,7 +19072,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B153" s="16"/>
       <c r="C153" s="22">
@@ -19111,7 +19117,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="18" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B154" s="19">
         <v>1960.12</v>
@@ -19188,7 +19194,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B155" s="16">
         <v>0.0</v>
@@ -19263,7 +19269,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B156" s="16"/>
       <c r="C156" s="16"/>
@@ -19296,7 +19302,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B157" s="22">
         <v>-0.01</v>
@@ -19331,7 +19337,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="18" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B158" s="20">
         <v>0.0</v>
@@ -19398,7 +19404,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="18" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B159" s="19">
         <v>1960.11</v>
@@ -19475,7 +19481,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B160" s="17">
         <v>0.01</v>
@@ -19520,7 +19526,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="18" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B161" s="19">
         <v>5884.97</v>
@@ -19597,7 +19603,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B162" s="17">
         <v>0.02</v>
@@ -19674,7 +19680,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B163" s="17">
         <v>16.98</v>
@@ -19751,7 +19757,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B164" s="17">
         <v>16.96</v>
@@ -19828,7 +19834,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B165" s="16"/>
       <c r="C165" s="16"/>
@@ -19867,7 +19873,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B166" s="16"/>
       <c r="C166" s="16"/>
@@ -19898,7 +19904,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B167" s="16"/>
       <c r="C167" s="16"/>
@@ -19943,7 +19949,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B168" s="16"/>
       <c r="C168" s="16"/>
@@ -19974,7 +19980,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B169" s="17">
         <v>61.16</v>
@@ -20029,7 +20035,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B170" s="17">
         <v>28.48</v>
@@ -20082,7 +20088,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B171" s="17">
         <v>19.99</v>
@@ -20135,7 +20141,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B172" s="17">
         <v>23.55</v>
@@ -20188,7 +20194,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B173" s="15">
         <v>278.95</v>
@@ -20243,7 +20249,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B174" s="15">
         <v>2736.84</v>
@@ -20280,7 +20286,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B175" s="15">
         <v>105.25</v>
@@ -20321,7 +20327,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B176" s="15">
         <v>100.58</v>
@@ -20362,7 +20368,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B177" s="17">
         <v>98.23</v>
@@ -20403,7 +20409,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B178" s="17">
         <v>98.25</v>
@@ -20444,7 +20450,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B179" s="16"/>
       <c r="C179" s="16"/>
@@ -20481,7 +20487,7 @@
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B180" s="16"/>
       <c r="C180" s="16"/>
@@ -20514,7 +20520,7 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B181" s="16"/>
       <c r="C181" s="16"/>
@@ -20545,7 +20551,7 @@
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B182" s="15">
         <v>118.14</v>
@@ -20582,7 +20588,7 @@
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B183" s="15">
         <v>354.42</v>
@@ -20619,7 +20625,7 @@
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B184" s="15">
         <v>472.56</v>
@@ -20658,7 +20664,7 @@
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B185" s="17">
         <v>1.0</v>
@@ -20735,7 +20741,7 @@
     </row>
     <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B186" s="17">
         <v>16.98</v>
@@ -20812,7 +20818,7 @@
     </row>
     <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B187" s="17">
         <v>0.02</v>
@@ -20889,7 +20895,7 @@
     </row>
     <row r="188" ht="15.0" customHeight="1">
       <c r="A188" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B188" s="17">
         <v>16.96</v>
@@ -20966,7 +20972,7 @@
     </row>
     <row r="189" ht="15.0" customHeight="1">
       <c r="A189" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B189" s="15">
         <v>721.0</v>
@@ -21033,7 +21039,7 @@
     </row>
     <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B190" s="16"/>
       <c r="C190" s="16"/>
@@ -21080,7 +21086,7 @@
     </row>
     <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B191" s="16"/>
       <c r="C191" s="16"/>
@@ -21125,7 +21131,7 @@
     </row>
     <row r="192" ht="15.0" customHeight="1">
       <c r="A192" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B192" s="16"/>
       <c r="C192" s="16"/>
@@ -21172,7 +21178,7 @@
     </row>
     <row r="193" ht="15.0" customHeight="1">
       <c r="A193" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B193" s="16"/>
       <c r="C193" s="16"/>
@@ -21219,7 +21225,7 @@
     </row>
     <row r="194" ht="15.0" customHeight="1">
       <c r="A194" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B194" s="15">
         <v>9831.0</v>
@@ -21280,7 +21286,7 @@
     </row>
     <row r="195" ht="15.0" customHeight="1">
       <c r="A195" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B195" s="15">
         <v>9123.96</v>
@@ -22162,7 +22168,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -22535,67 +22541,67 @@
         <v>46</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -22668,7 +22674,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -22810,7 +22816,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -22858,7 +22864,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -22906,7 +22912,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -22954,7 +22960,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -23044,7 +23050,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -23092,7 +23098,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B27" s="15">
         <v>8730.53</v>
@@ -23138,7 +23144,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -23166,7 +23172,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B29" s="21">
         <v>-8376.81</v>
@@ -23186,13 +23192,13 @@
       <c r="G29" s="21">
         <v>-9529.35</v>
       </c>
-      <c r="H29" s="26">
+      <c r="H29" s="27">
         <v>-10274.28</v>
       </c>
       <c r="I29" s="21">
         <v>-8999.87</v>
       </c>
-      <c r="J29" s="26">
+      <c r="J29" s="27">
         <v>-10249.79</v>
       </c>
       <c r="K29" s="16"/>
@@ -23210,7 +23216,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -23240,7 +23246,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -23288,7 +23294,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B32" s="17">
         <v>16.02</v>
@@ -23356,7 +23362,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -23404,7 +23410,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -23452,7 +23458,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -23500,7 +23506,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -23532,7 +23538,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -23564,7 +23570,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -23592,7 +23598,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -23620,7 +23626,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B40" s="17">
         <v>29.69</v>
@@ -23688,7 +23694,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B41" s="21">
         <v>-101.5</v>
@@ -23756,7 +23762,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B42" s="16">
         <v>0.0</v>
@@ -23824,7 +23830,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B43" s="15">
         <v>369.74</v>
@@ -23864,7 +23870,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B44" s="16"/>
       <c r="C44" s="16"/>
@@ -23904,7 +23910,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B45" s="16"/>
       <c r="C45" s="17">
@@ -23938,7 +23944,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="18" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B46" s="19">
         <v>297.94</v>
@@ -24006,7 +24012,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B47" s="22">
         <v>-67.73</v>
@@ -24052,7 +24058,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B48" s="17">
         <v>1.05</v>
@@ -24112,7 +24118,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B49" s="16">
         <v>0.0</v>
@@ -24174,7 +24180,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B50" s="16">
         <v>0.0</v>
@@ -24226,7 +24232,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -24272,7 +24278,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B52" s="15">
         <v>367.77</v>
@@ -24304,7 +24310,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
@@ -24352,7 +24358,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
@@ -24404,7 +24410,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B55" s="16"/>
       <c r="C55" s="16">
@@ -24448,7 +24454,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -24484,7 +24490,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
@@ -24522,7 +24528,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B58" s="16"/>
       <c r="C58" s="16"/>
@@ -24562,7 +24568,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
@@ -24592,7 +24598,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -24622,7 +24628,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B61" s="16"/>
       <c r="C61" s="16"/>
@@ -24656,7 +24662,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B62" s="16"/>
       <c r="C62" s="16"/>
@@ -24692,7 +24698,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B63" s="16"/>
       <c r="C63" s="16">
@@ -24730,7 +24736,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B64" s="16"/>
       <c r="C64" s="16"/>
@@ -24762,7 +24768,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B65" s="16"/>
       <c r="C65" s="16">
@@ -24800,7 +24806,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="18" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B66" s="19">
         <v>301.08</v>
@@ -24868,7 +24874,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B67" s="16"/>
       <c r="C67" s="16"/>
@@ -24914,7 +24920,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B68" s="16"/>
       <c r="C68" s="16"/>
@@ -24958,7 +24964,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B69" s="17">
         <v>35.69</v>
@@ -25026,7 +25032,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B70" s="16">
         <v>0.0</v>
@@ -25094,7 +25100,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B71" s="22">
         <v>-1.24</v>
@@ -25142,7 +25148,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B72" s="22">
         <v>-36.41</v>
@@ -25178,7 +25184,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
@@ -25208,7 +25214,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B74" s="16"/>
       <c r="C74" s="16"/>
@@ -25238,7 +25244,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B75" s="17">
         <v>45.51</v>
@@ -25306,7 +25312,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B76" s="16"/>
       <c r="C76" s="16"/>
@@ -25358,7 +25364,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="16"/>
@@ -25392,7 +25398,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B78" s="16"/>
       <c r="C78" s="16"/>
@@ -25426,7 +25432,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B79" s="16"/>
       <c r="C79" s="16"/>
@@ -25462,7 +25468,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B80" s="16"/>
       <c r="C80" s="16"/>
@@ -25520,7 +25526,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B81" s="16"/>
       <c r="C81" s="16"/>
@@ -25548,7 +25554,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B82" s="16"/>
       <c r="C82" s="16"/>
@@ -25576,7 +25582,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B83" s="16"/>
       <c r="C83" s="16"/>
@@ -25604,7 +25610,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B84" s="15">
         <v>263.31</v>
@@ -25632,7 +25638,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B85" s="21">
         <v>-185.66</v>
@@ -25660,7 +25666,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B86" s="22">
         <v>-8.96</v>
@@ -25688,7 +25694,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B87" s="17">
         <v>69.47</v>
@@ -25716,7 +25722,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B88" s="16"/>
       <c r="C88" s="16"/>
@@ -25750,7 +25756,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B89" s="16"/>
       <c r="C89" s="16"/>
@@ -25790,7 +25796,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B90" s="22">
         <v>-40.09</v>
@@ -25830,7 +25836,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B91" s="16"/>
       <c r="C91" s="16"/>
@@ -25860,7 +25866,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B92" s="17">
         <v>0.01</v>
@@ -25898,7 +25904,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="18" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B93" s="19">
         <v>141.62</v>
@@ -25966,7 +25972,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B94" s="15">
         <v>478.98</v>
@@ -26034,7 +26040,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B95" s="15">
         <v>1226.66</v>
@@ -26102,7 +26108,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B96" s="15">
         <v>740.64</v>
@@ -26154,7 +26160,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B97" s="16">
         <v>0.0</v>
@@ -26206,7 +26212,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B98" s="16"/>
       <c r="C98" s="16"/>
@@ -26240,7 +26246,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B99" s="19">
         <v>740.64</v>
@@ -26308,7 +26314,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B100" s="16"/>
       <c r="C100" s="16"/>
@@ -27258,7 +27264,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -27821,7 +27827,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -27926,2591 +27932,2591 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="27" t="s">
-        <v>441</v>
-      </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="28"/>
-      <c r="W20" s="28"/>
-      <c r="X20" s="28"/>
-      <c r="Y20" s="28"/>
+      <c r="A20" s="28" t="s">
+        <v>442</v>
+      </c>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="29"/>
+      <c r="X20" s="29"/>
+      <c r="Y20" s="29"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="29" t="s">
-        <v>441</v>
-      </c>
-      <c r="B21" s="30">
+      <c r="A21" s="30" t="s">
+        <v>442</v>
+      </c>
+      <c r="B21" s="31">
         <v>1530.23</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <v>2063.0</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <v>1886.95</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <v>1520.63</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <v>3097.23</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="31">
         <v>4622.88</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="31">
         <v>4942.75</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="31">
         <v>3793.48</v>
       </c>
-      <c r="J21" s="30">
+      <c r="J21" s="31">
         <v>5058.46</v>
       </c>
-      <c r="K21" s="30">
+      <c r="K21" s="31">
         <v>5203.53</v>
       </c>
-      <c r="L21" s="30">
+      <c r="L21" s="31">
         <v>4023.96</v>
       </c>
-      <c r="M21" s="30">
+      <c r="M21" s="31">
         <v>2811.17</v>
       </c>
-      <c r="N21" s="30">
+      <c r="N21" s="31">
         <v>3046.43</v>
       </c>
-      <c r="O21" s="30">
+      <c r="O21" s="31">
         <v>3199.44</v>
       </c>
-      <c r="P21" s="30">
+      <c r="P21" s="31">
         <v>3267.59</v>
       </c>
-      <c r="Q21" s="30">
+      <c r="Q21" s="31">
         <v>3654.64</v>
       </c>
-      <c r="R21" s="30">
+      <c r="R21" s="31">
         <v>3319.74</v>
       </c>
-      <c r="S21" s="30">
+      <c r="S21" s="31">
         <v>2925.42</v>
       </c>
-      <c r="T21" s="30">
+      <c r="T21" s="31">
         <v>1828.31</v>
       </c>
-      <c r="U21" s="31"/>
-      <c r="V21" s="31"/>
-      <c r="W21" s="31"/>
-      <c r="X21" s="31"/>
-      <c r="Y21" s="31"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="32"/>
+      <c r="X21" s="32"/>
+      <c r="Y21" s="32"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="29" t="s">
-        <v>442</v>
-      </c>
-      <c r="B22" s="30">
+      <c r="A22" s="30" t="s">
+        <v>443</v>
+      </c>
+      <c r="B22" s="31">
         <v>2192.58</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <v>2917.51</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="31">
         <v>3504.65</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="31">
         <v>3734.18</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="31">
         <v>4304.16</v>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="31">
         <v>5056.46</v>
       </c>
-      <c r="H22" s="30">
+      <c r="H22" s="31">
         <v>4706.16</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="31">
         <v>4359.23</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="31">
         <v>4297.21</v>
       </c>
-      <c r="K22" s="30">
+      <c r="K22" s="31">
         <v>3821.82</v>
       </c>
-      <c r="L22" s="30">
+      <c r="L22" s="31">
         <v>3751.27</v>
       </c>
-      <c r="M22" s="30">
+      <c r="M22" s="31">
         <v>3622.6</v>
       </c>
-      <c r="N22" s="30">
+      <c r="N22" s="31">
         <v>3490.59</v>
       </c>
-      <c r="O22" s="30">
+      <c r="O22" s="31">
         <v>2978.69</v>
       </c>
-      <c r="P22" s="30">
+      <c r="P22" s="31">
         <v>2822.07</v>
       </c>
-      <c r="Q22" s="31"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
-      <c r="X22" s="31"/>
-      <c r="Y22" s="31"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="32"/>
+      <c r="V22" s="32"/>
+      <c r="W22" s="32"/>
+      <c r="X22" s="32"/>
+      <c r="Y22" s="32"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="27" t="s">
-        <v>443</v>
-      </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="28"/>
-      <c r="V23" s="28"/>
-      <c r="W23" s="28"/>
-      <c r="X23" s="28"/>
-      <c r="Y23" s="28"/>
+      <c r="A23" s="28" t="s">
+        <v>444</v>
+      </c>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+      <c r="W23" s="29"/>
+      <c r="X23" s="29"/>
+      <c r="Y23" s="29"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="29" t="s">
-        <v>443</v>
-      </c>
-      <c r="B24" s="30">
+      <c r="A24" s="30" t="s">
+        <v>444</v>
+      </c>
+      <c r="B24" s="31">
         <v>858.69</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <v>931.21</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <v>774.99</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="31">
         <v>676.58</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="31">
         <v>1395.59</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="31">
         <v>1636.72</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="31">
         <v>809.68</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="31">
         <v>1019.0</v>
       </c>
-      <c r="J24" s="30">
+      <c r="J24" s="31">
         <v>2144.25</v>
       </c>
-      <c r="K24" s="30">
+      <c r="K24" s="31">
         <v>2982.93</v>
       </c>
-      <c r="L24" s="30">
+      <c r="L24" s="31">
         <v>1800.47</v>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="31">
         <v>940.54</v>
       </c>
-      <c r="N24" s="30">
+      <c r="N24" s="31">
         <v>1241.65</v>
       </c>
-      <c r="O24" s="30">
+      <c r="O24" s="31">
         <v>879.79</v>
       </c>
-      <c r="P24" s="30">
+      <c r="P24" s="31">
         <v>1137.87</v>
       </c>
-      <c r="Q24" s="30">
+      <c r="Q24" s="31">
         <v>1898.48</v>
       </c>
-      <c r="R24" s="30">
+      <c r="R24" s="31">
         <v>1796.16</v>
       </c>
-      <c r="S24" s="30">
+      <c r="S24" s="31">
         <v>1238.63</v>
       </c>
-      <c r="T24" s="30">
+      <c r="T24" s="31">
         <v>1463.45</v>
       </c>
-      <c r="U24" s="31"/>
-      <c r="V24" s="31"/>
-      <c r="W24" s="31"/>
-      <c r="X24" s="31"/>
-      <c r="Y24" s="31"/>
+      <c r="U24" s="32"/>
+      <c r="V24" s="32"/>
+      <c r="W24" s="32"/>
+      <c r="X24" s="32"/>
+      <c r="Y24" s="32"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="29" t="s">
-        <v>444</v>
-      </c>
-      <c r="B25" s="30">
+      <c r="A25" s="30" t="s">
+        <v>445</v>
+      </c>
+      <c r="B25" s="31">
         <v>1004.29</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <v>1196.91</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="31">
         <v>1144.75</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="31">
         <v>1143.4</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="31">
         <v>1398.72</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="31">
         <v>1859.88</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="31">
         <v>1808.68</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="31">
         <v>1864.16</v>
       </c>
-      <c r="J25" s="30">
+      <c r="J25" s="31">
         <v>1943.09</v>
       </c>
-      <c r="K25" s="30">
+      <c r="K25" s="31">
         <v>1614.25</v>
       </c>
-      <c r="L25" s="30">
+      <c r="L25" s="31">
         <v>1358.32</v>
       </c>
-      <c r="M25" s="30">
+      <c r="M25" s="31">
         <v>1380.57</v>
       </c>
-      <c r="N25" s="30">
+      <c r="N25" s="31">
         <v>1461.16</v>
       </c>
-      <c r="O25" s="30">
+      <c r="O25" s="31">
         <v>1254.91</v>
       </c>
-      <c r="P25" s="30">
+      <c r="P25" s="31">
         <v>1422.9</v>
       </c>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="31"/>
-      <c r="S25" s="31"/>
-      <c r="T25" s="31"/>
-      <c r="U25" s="31"/>
-      <c r="V25" s="31"/>
-      <c r="W25" s="31"/>
-      <c r="X25" s="31"/>
-      <c r="Y25" s="31"/>
+      <c r="Q25" s="32"/>
+      <c r="R25" s="32"/>
+      <c r="S25" s="32"/>
+      <c r="T25" s="32"/>
+      <c r="U25" s="32"/>
+      <c r="V25" s="32"/>
+      <c r="W25" s="32"/>
+      <c r="X25" s="32"/>
+      <c r="Y25" s="32"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="27" t="s">
-        <v>445</v>
-      </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="28"/>
-      <c r="U26" s="28"/>
-      <c r="V26" s="28"/>
-      <c r="W26" s="28"/>
-      <c r="X26" s="28"/>
-      <c r="Y26" s="28"/>
+      <c r="A26" s="28" t="s">
+        <v>446</v>
+      </c>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
+      <c r="W26" s="29"/>
+      <c r="X26" s="29"/>
+      <c r="Y26" s="29"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="29" t="s">
-        <v>446</v>
-      </c>
-      <c r="B27" s="32">
+      <c r="A27" s="30" t="s">
+        <v>447</v>
+      </c>
+      <c r="B27" s="33">
         <v>50.56</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <v>54.83</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="33">
         <v>45.63</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="33">
         <v>39.84</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <v>132.35</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="31">
         <v>155.22</v>
       </c>
-      <c r="H27" s="30">
+      <c r="H27" s="31">
         <v>245.22</v>
       </c>
-      <c r="I27" s="30">
+      <c r="I27" s="31">
         <v>308.62</v>
       </c>
-      <c r="J27" s="30">
+      <c r="J27" s="31">
         <v>649.41</v>
       </c>
-      <c r="K27" s="30">
+      <c r="K27" s="31">
         <v>903.42</v>
       </c>
-      <c r="L27" s="30">
+      <c r="L27" s="31">
         <v>545.29</v>
       </c>
-      <c r="M27" s="30">
+      <c r="M27" s="31">
         <v>388.14</v>
       </c>
-      <c r="N27" s="30">
+      <c r="N27" s="31">
         <v>512.4</v>
       </c>
-      <c r="O27" s="30">
+      <c r="O27" s="31">
         <v>363.07</v>
       </c>
-      <c r="P27" s="30">
+      <c r="P27" s="31">
         <v>469.57</v>
       </c>
-      <c r="Q27" s="30">
+      <c r="Q27" s="31">
         <v>783.46</v>
       </c>
-      <c r="R27" s="30">
+      <c r="R27" s="31">
         <v>741.23</v>
       </c>
-      <c r="S27" s="30">
+      <c r="S27" s="31">
         <v>511.15</v>
       </c>
-      <c r="T27" s="30">
+      <c r="T27" s="31">
         <v>603.93</v>
       </c>
-      <c r="U27" s="31"/>
-      <c r="V27" s="31"/>
-      <c r="W27" s="31"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="31"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="32"/>
+      <c r="X27" s="32"/>
+      <c r="Y27" s="32"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="29" t="s">
-        <v>447</v>
-      </c>
-      <c r="B28" s="32">
+      <c r="A28" s="30" t="s">
+        <v>448</v>
+      </c>
+      <c r="B28" s="33">
         <v>70.98</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <v>95.49</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="31">
         <v>136.09</v>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="31">
         <v>184.32</v>
       </c>
-      <c r="F28" s="30">
+      <c r="F28" s="31">
         <v>300.48</v>
       </c>
-      <c r="G28" s="30">
+      <c r="G28" s="31">
         <v>495.19</v>
       </c>
-      <c r="H28" s="30">
+      <c r="H28" s="31">
         <v>547.78</v>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="31">
         <v>587.22</v>
       </c>
-      <c r="J28" s="30">
+      <c r="J28" s="31">
         <v>643.18</v>
       </c>
-      <c r="K28" s="30">
+      <c r="K28" s="31">
         <v>563.25</v>
       </c>
-      <c r="L28" s="30">
+      <c r="L28" s="31">
         <v>521.0</v>
       </c>
-      <c r="M28" s="30">
+      <c r="M28" s="31">
         <v>569.73</v>
       </c>
-      <c r="N28" s="30">
+      <c r="N28" s="31">
         <v>602.98</v>
       </c>
-      <c r="O28" s="30">
+      <c r="O28" s="31">
         <v>517.87</v>
       </c>
-      <c r="P28" s="30">
+      <c r="P28" s="31">
         <v>587.2</v>
       </c>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="31"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="32"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="32"/>
+      <c r="X28" s="32"/>
+      <c r="Y28" s="32"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="27" t="s">
-        <v>448</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
-      <c r="U29" s="28"/>
-      <c r="V29" s="28"/>
-      <c r="W29" s="28"/>
-      <c r="X29" s="28"/>
-      <c r="Y29" s="28"/>
+      <c r="A29" s="28" t="s">
+        <v>449</v>
+      </c>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="29"/>
+      <c r="X29" s="29"/>
+      <c r="Y29" s="29"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="29" t="s">
-        <v>449</v>
-      </c>
-      <c r="B30" s="33">
+      <c r="A30" s="30" t="s">
+        <v>450</v>
+      </c>
+      <c r="B30" s="34">
         <v>14.41</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="35">
         <v>-2.81</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="35">
         <v>-1.84</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="35">
         <v>-25.04</v>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="34">
         <v>48.65</v>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="34">
         <v>43.65</v>
       </c>
-      <c r="H30" s="34">
+      <c r="H30" s="35">
         <v>-20.89</v>
       </c>
-      <c r="I30" s="33">
+      <c r="I30" s="34">
         <v>16.87</v>
       </c>
-      <c r="J30" s="34">
+      <c r="J30" s="35">
         <v>-18.63</v>
       </c>
-      <c r="K30" s="33">
+      <c r="K30" s="34">
         <v>6.93</v>
       </c>
-      <c r="L30" s="33">
+      <c r="L30" s="34">
         <v>56.75</v>
       </c>
-      <c r="M30" s="33">
+      <c r="M30" s="34">
         <v>52.21</v>
       </c>
-      <c r="N30" s="33">
+      <c r="N30" s="34">
         <v>32.88</v>
       </c>
-      <c r="O30" s="34">
+      <c r="O30" s="35">
         <v>-31.73</v>
       </c>
-      <c r="P30" s="34">
+      <c r="P30" s="35">
         <v>-2.11</v>
       </c>
-      <c r="Q30" s="34">
+      <c r="Q30" s="35">
         <v>-8.76</v>
       </c>
-      <c r="R30" s="34">
+      <c r="R30" s="35">
         <v>-5.9</v>
       </c>
-      <c r="S30" s="34">
+      <c r="S30" s="35">
         <v>-104.19</v>
       </c>
-      <c r="T30" s="34">
+      <c r="T30" s="35">
         <v>-26.34</v>
       </c>
-      <c r="U30" s="33"/>
-      <c r="V30" s="33"/>
-      <c r="W30" s="33"/>
-      <c r="X30" s="33"/>
-      <c r="Y30" s="33"/>
+      <c r="U30" s="34"/>
+      <c r="V30" s="34"/>
+      <c r="W30" s="34"/>
+      <c r="X30" s="34"/>
+      <c r="Y30" s="34"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="29" t="s">
-        <v>450</v>
-      </c>
-      <c r="B31" s="33">
+      <c r="A31" s="30" t="s">
+        <v>451</v>
+      </c>
+      <c r="B31" s="34">
         <v>19.61</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="34">
         <v>28.94</v>
       </c>
-      <c r="D31" s="33">
+      <c r="D31" s="34">
         <v>10.96</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="34">
         <v>13.65</v>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="34">
         <v>0.44</v>
       </c>
-      <c r="G31" s="33">
+      <c r="G31" s="34">
         <v>0.48</v>
       </c>
-      <c r="H31" s="33">
+      <c r="H31" s="34">
         <v>9.66</v>
       </c>
-      <c r="I31" s="33">
+      <c r="I31" s="34">
         <v>18.39</v>
       </c>
-      <c r="J31" s="33">
+      <c r="J31" s="34">
         <v>21.26</v>
       </c>
-      <c r="K31" s="33">
+      <c r="K31" s="34">
         <v>21.3</v>
       </c>
-      <c r="L31" s="33">
+      <c r="L31" s="34">
         <v>21.33</v>
       </c>
-      <c r="M31" s="33">
+      <c r="M31" s="34">
         <v>5.34</v>
       </c>
-      <c r="N31" s="34">
+      <c r="N31" s="35">
         <v>-3.0</v>
       </c>
-      <c r="O31" s="34">
+      <c r="O31" s="35">
         <v>-24.35</v>
       </c>
-      <c r="P31" s="34">
+      <c r="P31" s="35">
         <v>-23.79</v>
       </c>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="33"/>
-      <c r="S31" s="33"/>
-      <c r="T31" s="33"/>
-      <c r="U31" s="33"/>
-      <c r="V31" s="33"/>
-      <c r="W31" s="33"/>
-      <c r="X31" s="33"/>
-      <c r="Y31" s="33"/>
+      <c r="Q31" s="34"/>
+      <c r="R31" s="34"/>
+      <c r="S31" s="34"/>
+      <c r="T31" s="34"/>
+      <c r="U31" s="34"/>
+      <c r="V31" s="34"/>
+      <c r="W31" s="34"/>
+      <c r="X31" s="34"/>
+      <c r="Y31" s="34"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="27" t="s">
-        <v>451</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="28"/>
-      <c r="Y32" s="28"/>
+      <c r="A32" s="28" t="s">
+        <v>452</v>
+      </c>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="29"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="29"/>
+      <c r="T32" s="29"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="29"/>
+      <c r="W32" s="29"/>
+      <c r="X32" s="29"/>
+      <c r="Y32" s="29"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="29" t="s">
-        <v>452</v>
-      </c>
-      <c r="B33" s="33">
+      <c r="A33" s="30" t="s">
+        <v>453</v>
+      </c>
+      <c r="B33" s="34">
         <v>0.0</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="34">
         <v>0.0</v>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="34">
         <v>0.0</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="34">
         <v>0.0</v>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="34">
         <v>0.0</v>
       </c>
-      <c r="G33" s="33">
+      <c r="G33" s="34">
         <v>0.0</v>
       </c>
-      <c r="H33" s="33">
+      <c r="H33" s="34">
         <v>0.0</v>
       </c>
-      <c r="I33" s="33">
+      <c r="I33" s="34">
         <v>3.53</v>
       </c>
-      <c r="J33" s="33">
+      <c r="J33" s="34">
         <v>2.78</v>
       </c>
-      <c r="K33" s="33">
+      <c r="K33" s="34">
         <v>1.84</v>
       </c>
-      <c r="L33" s="33">
+      <c r="L33" s="34">
         <v>3.21</v>
       </c>
-      <c r="M33" s="33">
+      <c r="M33" s="34">
         <v>4.24</v>
       </c>
-      <c r="N33" s="33">
+      <c r="N33" s="34">
         <v>1.48</v>
       </c>
-      <c r="O33" s="33">
+      <c r="O33" s="34">
         <v>3.68</v>
       </c>
-      <c r="P33" s="33">
+      <c r="P33" s="34">
         <v>2.41</v>
       </c>
-      <c r="Q33" s="33">
+      <c r="Q33" s="34">
         <v>1.46</v>
       </c>
-      <c r="R33" s="33">
+      <c r="R33" s="34">
         <v>1.64</v>
       </c>
-      <c r="S33" s="33">
+      <c r="S33" s="34">
         <v>2.78</v>
       </c>
-      <c r="T33" s="33">
+      <c r="T33" s="34">
         <v>0.0</v>
       </c>
-      <c r="U33" s="33"/>
-      <c r="V33" s="33"/>
-      <c r="W33" s="33"/>
-      <c r="X33" s="33"/>
-      <c r="Y33" s="33"/>
+      <c r="U33" s="34"/>
+      <c r="V33" s="34"/>
+      <c r="W33" s="34"/>
+      <c r="X33" s="34"/>
+      <c r="Y33" s="34"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="29" t="s">
-        <v>453</v>
-      </c>
-      <c r="B34" s="33">
+      <c r="A34" s="30" t="s">
+        <v>454</v>
+      </c>
+      <c r="B34" s="34">
         <v>0.0</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="34">
         <v>0.0</v>
       </c>
-      <c r="D34" s="33">
+      <c r="D34" s="34">
         <v>0.0</v>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="34">
         <v>1.25</v>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="34">
         <v>1.95</v>
       </c>
-      <c r="G34" s="33">
+      <c r="G34" s="34">
         <v>2.02</v>
       </c>
-      <c r="H34" s="33">
+      <c r="H34" s="34">
         <v>2.37</v>
       </c>
-      <c r="I34" s="33">
+      <c r="I34" s="34">
         <v>2.84</v>
       </c>
-      <c r="J34" s="33">
+      <c r="J34" s="34">
         <v>2.52</v>
       </c>
-      <c r="K34" s="33">
+      <c r="K34" s="34">
         <v>2.65</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="34">
         <v>2.89</v>
       </c>
-      <c r="M34" s="33">
+      <c r="M34" s="34">
         <v>2.37</v>
       </c>
-      <c r="N34" s="33">
+      <c r="N34" s="34">
         <v>1.97</v>
       </c>
-      <c r="O34" s="33">
+      <c r="O34" s="34">
         <v>2.18</v>
       </c>
-      <c r="P34" s="33">
+      <c r="P34" s="34">
         <v>1.54</v>
       </c>
-      <c r="Q34" s="33"/>
-      <c r="R34" s="33"/>
-      <c r="S34" s="33"/>
-      <c r="T34" s="33"/>
-      <c r="U34" s="33"/>
-      <c r="V34" s="33"/>
-      <c r="W34" s="33"/>
-      <c r="X34" s="33"/>
-      <c r="Y34" s="33"/>
+      <c r="Q34" s="34"/>
+      <c r="R34" s="34"/>
+      <c r="S34" s="34"/>
+      <c r="T34" s="34"/>
+      <c r="U34" s="34"/>
+      <c r="V34" s="34"/>
+      <c r="W34" s="34"/>
+      <c r="X34" s="34"/>
+      <c r="Y34" s="34"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="29" t="s">
-        <v>454</v>
-      </c>
-      <c r="B35" s="33">
+      <c r="A35" s="30" t="s">
+        <v>455</v>
+      </c>
+      <c r="B35" s="34">
         <v>0.0</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="34">
         <v>0.0</v>
       </c>
-      <c r="D35" s="33">
+      <c r="D35" s="34">
         <v>0.0</v>
       </c>
-      <c r="E35" s="33">
+      <c r="E35" s="34">
         <v>0.0</v>
       </c>
-      <c r="F35" s="33">
+      <c r="F35" s="34">
         <v>0.0</v>
       </c>
-      <c r="G35" s="33">
+      <c r="G35" s="34">
         <v>0.0</v>
       </c>
-      <c r="H35" s="33">
+      <c r="H35" s="34">
         <v>0.0</v>
       </c>
-      <c r="I35" s="33">
+      <c r="I35" s="34">
         <v>3.53</v>
       </c>
-      <c r="J35" s="33">
+      <c r="J35" s="34">
         <v>2.78</v>
       </c>
-      <c r="K35" s="33">
+      <c r="K35" s="34">
         <v>1.84</v>
       </c>
-      <c r="L35" s="33">
+      <c r="L35" s="34">
         <v>3.21</v>
       </c>
-      <c r="M35" s="33">
+      <c r="M35" s="34">
         <v>4.24</v>
       </c>
-      <c r="N35" s="33">
+      <c r="N35" s="34">
         <v>1.48</v>
       </c>
-      <c r="O35" s="33">
+      <c r="O35" s="34">
         <v>3.68</v>
       </c>
-      <c r="P35" s="33">
+      <c r="P35" s="34">
         <v>3.0</v>
       </c>
-      <c r="Q35" s="33">
+      <c r="Q35" s="34">
         <v>1.81</v>
       </c>
-      <c r="R35" s="33">
+      <c r="R35" s="34">
         <v>2.04</v>
       </c>
-      <c r="S35" s="33">
+      <c r="S35" s="34">
         <v>3.46</v>
       </c>
-      <c r="T35" s="33">
+      <c r="T35" s="34">
         <v>0.0</v>
       </c>
-      <c r="U35" s="33"/>
-      <c r="V35" s="33"/>
-      <c r="W35" s="33"/>
-      <c r="X35" s="33"/>
-      <c r="Y35" s="33"/>
+      <c r="U35" s="34"/>
+      <c r="V35" s="34"/>
+      <c r="W35" s="34"/>
+      <c r="X35" s="34"/>
+      <c r="Y35" s="34"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="29" t="s">
-        <v>455</v>
-      </c>
-      <c r="B36" s="33">
+      <c r="A36" s="30" t="s">
+        <v>456</v>
+      </c>
+      <c r="B36" s="34">
         <v>0.0</v>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="34">
         <v>0.0</v>
       </c>
-      <c r="D36" s="33">
+      <c r="D36" s="34">
         <v>0.0</v>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="34">
         <v>1.25</v>
       </c>
-      <c r="F36" s="33">
+      <c r="F36" s="34">
         <v>1.95</v>
       </c>
-      <c r="G36" s="33">
+      <c r="G36" s="34">
         <v>2.02</v>
       </c>
-      <c r="H36" s="33">
+      <c r="H36" s="34">
         <v>2.37</v>
       </c>
-      <c r="I36" s="33">
+      <c r="I36" s="34">
         <v>2.84</v>
       </c>
-      <c r="J36" s="33">
+      <c r="J36" s="34">
         <v>2.52</v>
       </c>
-      <c r="K36" s="33">
+      <c r="K36" s="34">
         <v>2.65</v>
       </c>
-      <c r="L36" s="33">
+      <c r="L36" s="34">
         <v>3.02</v>
       </c>
-      <c r="M36" s="33">
+      <c r="M36" s="34">
         <v>2.6</v>
       </c>
-      <c r="N36" s="33">
+      <c r="N36" s="34">
         <v>2.27</v>
       </c>
-      <c r="O36" s="33">
+      <c r="O36" s="34">
         <v>2.58</v>
       </c>
-      <c r="P36" s="33">
+      <c r="P36" s="34">
         <v>1.92</v>
       </c>
-      <c r="Q36" s="33"/>
-      <c r="R36" s="33"/>
-      <c r="S36" s="33"/>
-      <c r="T36" s="33"/>
-      <c r="U36" s="33"/>
-      <c r="V36" s="33"/>
-      <c r="W36" s="33"/>
-      <c r="X36" s="33"/>
-      <c r="Y36" s="33"/>
+      <c r="Q36" s="34"/>
+      <c r="R36" s="34"/>
+      <c r="S36" s="34"/>
+      <c r="T36" s="34"/>
+      <c r="U36" s="34"/>
+      <c r="V36" s="34"/>
+      <c r="W36" s="34"/>
+      <c r="X36" s="34"/>
+      <c r="Y36" s="34"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="27" t="s">
-        <v>456</v>
-      </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
-      <c r="U37" s="28"/>
-      <c r="V37" s="28"/>
-      <c r="W37" s="28"/>
-      <c r="X37" s="28"/>
-      <c r="Y37" s="28"/>
+      <c r="A37" s="28" t="s">
+        <v>457</v>
+      </c>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="29"/>
+      <c r="T37" s="29"/>
+      <c r="U37" s="29"/>
+      <c r="V37" s="29"/>
+      <c r="W37" s="29"/>
+      <c r="X37" s="29"/>
+      <c r="Y37" s="29"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="29" t="s">
-        <v>457</v>
-      </c>
-      <c r="B38" s="32">
+      <c r="A38" s="30" t="s">
+        <v>458</v>
+      </c>
+      <c r="B38" s="33">
         <v>0.61</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="33">
         <v>0.7</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="33">
         <v>0.66</v>
       </c>
-      <c r="E38" s="32">
+      <c r="E38" s="33">
         <v>0.57</v>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="33">
         <v>0.93</v>
       </c>
-      <c r="G38" s="32">
+      <c r="G38" s="33">
         <v>0.92</v>
       </c>
-      <c r="H38" s="32">
+      <c r="H38" s="33">
         <v>0.86</v>
       </c>
-      <c r="I38" s="32">
+      <c r="I38" s="33">
         <v>0.53</v>
       </c>
-      <c r="J38" s="32">
+      <c r="J38" s="33">
         <v>0.89</v>
       </c>
-      <c r="K38" s="32">
+      <c r="K38" s="33">
         <v>1.28</v>
       </c>
-      <c r="L38" s="32">
+      <c r="L38" s="33">
         <v>0.79</v>
       </c>
-      <c r="M38" s="32">
+      <c r="M38" s="33">
         <v>0.56</v>
       </c>
-      <c r="N38" s="32">
+      <c r="N38" s="33">
         <v>0.81</v>
       </c>
-      <c r="O38" s="32">
+      <c r="O38" s="33">
         <v>0.7</v>
       </c>
-      <c r="P38" s="32">
+      <c r="P38" s="33">
         <v>0.85</v>
       </c>
-      <c r="Q38" s="32">
+      <c r="Q38" s="33">
         <v>1.45</v>
       </c>
-      <c r="R38" s="32">
+      <c r="R38" s="33">
         <v>1.32</v>
       </c>
-      <c r="S38" s="32">
+      <c r="S38" s="33">
         <v>0.77</v>
       </c>
-      <c r="T38" s="32">
+      <c r="T38" s="33">
         <v>1.19</v>
       </c>
-      <c r="U38" s="31"/>
-      <c r="V38" s="31"/>
-      <c r="W38" s="31"/>
-      <c r="X38" s="31"/>
-      <c r="Y38" s="31"/>
+      <c r="U38" s="32"/>
+      <c r="V38" s="32"/>
+      <c r="W38" s="32"/>
+      <c r="X38" s="32"/>
+      <c r="Y38" s="32"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="29" t="s">
-        <v>458</v>
-      </c>
-      <c r="B39" s="32">
+      <c r="A39" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="B39" s="33">
         <v>0.74</v>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="33">
         <v>0.81</v>
       </c>
-      <c r="D39" s="32">
+      <c r="D39" s="33">
         <v>0.84</v>
       </c>
-      <c r="E39" s="32">
+      <c r="E39" s="33">
         <v>0.7</v>
       </c>
-      <c r="F39" s="32">
+      <c r="F39" s="33">
         <v>0.78</v>
       </c>
-      <c r="G39" s="32">
+      <c r="G39" s="33">
         <v>0.92</v>
       </c>
-      <c r="H39" s="32">
+      <c r="H39" s="33">
         <v>0.89</v>
       </c>
-      <c r="I39" s="32">
+      <c r="I39" s="33">
         <v>0.83</v>
       </c>
-      <c r="J39" s="32">
+      <c r="J39" s="33">
         <v>0.87</v>
       </c>
-      <c r="K39" s="32">
+      <c r="K39" s="33">
         <v>0.84</v>
       </c>
-      <c r="L39" s="32">
+      <c r="L39" s="33">
         <v>0.74</v>
       </c>
-      <c r="M39" s="32">
+      <c r="M39" s="33">
         <v>0.87</v>
       </c>
-      <c r="N39" s="32">
+      <c r="N39" s="33">
         <v>1.02</v>
       </c>
-      <c r="O39" s="32">
+      <c r="O39" s="33">
         <v>1.02</v>
       </c>
-      <c r="P39" s="32">
+      <c r="P39" s="33">
         <v>1.11</v>
       </c>
-      <c r="Q39" s="31"/>
-      <c r="R39" s="31"/>
-      <c r="S39" s="31"/>
-      <c r="T39" s="31"/>
-      <c r="U39" s="31"/>
-      <c r="V39" s="31"/>
-      <c r="W39" s="31"/>
-      <c r="X39" s="31"/>
-      <c r="Y39" s="31"/>
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
+      <c r="U39" s="32"/>
+      <c r="V39" s="32"/>
+      <c r="W39" s="32"/>
+      <c r="X39" s="32"/>
+      <c r="Y39" s="32"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="27" t="s">
-        <v>459</v>
-      </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28"/>
-      <c r="T40" s="28"/>
-      <c r="U40" s="28"/>
-      <c r="V40" s="28"/>
-      <c r="W40" s="28"/>
-      <c r="X40" s="28"/>
-      <c r="Y40" s="28"/>
+      <c r="A40" s="28" t="s">
+        <v>460</v>
+      </c>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="29"/>
+      <c r="S40" s="29"/>
+      <c r="T40" s="29"/>
+      <c r="U40" s="29"/>
+      <c r="V40" s="29"/>
+      <c r="W40" s="29"/>
+      <c r="X40" s="29"/>
+      <c r="Y40" s="29"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="29" t="s">
-        <v>460</v>
-      </c>
-      <c r="B41" s="32">
+      <c r="A41" s="30" t="s">
+        <v>461</v>
+      </c>
+      <c r="B41" s="33">
         <v>0.62</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="33">
         <v>0.71</v>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="33">
         <v>0.67</v>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="33">
         <v>0.58</v>
       </c>
-      <c r="F41" s="32">
+      <c r="F41" s="33">
         <v>0.94</v>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="33">
         <v>0.93</v>
       </c>
-      <c r="H41" s="32">
+      <c r="H41" s="33">
         <v>0.89</v>
       </c>
-      <c r="I41" s="32">
+      <c r="I41" s="33">
         <v>0.54</v>
       </c>
-      <c r="J41" s="32">
+      <c r="J41" s="33">
         <v>0.91</v>
       </c>
-      <c r="K41" s="32">
+      <c r="K41" s="33">
         <v>1.3</v>
       </c>
-      <c r="L41" s="32">
+      <c r="L41" s="33">
         <v>0.81</v>
       </c>
-      <c r="M41" s="32">
+      <c r="M41" s="33">
         <v>0.57</v>
       </c>
-      <c r="N41" s="32">
+      <c r="N41" s="33">
         <v>0.83</v>
       </c>
-      <c r="O41" s="32">
+      <c r="O41" s="33">
         <v>0.72</v>
       </c>
-      <c r="P41" s="32">
+      <c r="P41" s="33">
         <v>0.87</v>
       </c>
-      <c r="Q41" s="32">
+      <c r="Q41" s="33">
         <v>1.47</v>
       </c>
-      <c r="R41" s="32">
+      <c r="R41" s="33">
         <v>1.33</v>
       </c>
-      <c r="S41" s="32">
+      <c r="S41" s="33">
         <v>0.78</v>
       </c>
-      <c r="T41" s="32">
+      <c r="T41" s="33">
         <v>1.2</v>
       </c>
-      <c r="U41" s="31"/>
-      <c r="V41" s="31"/>
-      <c r="W41" s="31"/>
-      <c r="X41" s="31"/>
-      <c r="Y41" s="31"/>
+      <c r="U41" s="32"/>
+      <c r="V41" s="32"/>
+      <c r="W41" s="32"/>
+      <c r="X41" s="32"/>
+      <c r="Y41" s="32"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="29" t="s">
-        <v>461</v>
-      </c>
-      <c r="B42" s="32">
+      <c r="A42" s="30" t="s">
+        <v>462</v>
+      </c>
+      <c r="B42" s="33">
         <v>0.75</v>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="33">
         <v>0.83</v>
       </c>
-      <c r="D42" s="32">
+      <c r="D42" s="33">
         <v>0.86</v>
       </c>
-      <c r="E42" s="32">
+      <c r="E42" s="33">
         <v>0.72</v>
       </c>
-      <c r="F42" s="32">
+      <c r="F42" s="33">
         <v>0.8</v>
       </c>
-      <c r="G42" s="32">
+      <c r="G42" s="33">
         <v>0.94</v>
       </c>
-      <c r="H42" s="32">
+      <c r="H42" s="33">
         <v>0.91</v>
       </c>
-      <c r="I42" s="32">
+      <c r="I42" s="33">
         <v>0.84</v>
       </c>
-      <c r="J42" s="32">
+      <c r="J42" s="33">
         <v>0.88</v>
       </c>
-      <c r="K42" s="32">
+      <c r="K42" s="33">
         <v>0.85</v>
       </c>
-      <c r="L42" s="32">
+      <c r="L42" s="33">
         <v>0.75</v>
       </c>
-      <c r="M42" s="32">
+      <c r="M42" s="33">
         <v>0.88</v>
       </c>
-      <c r="N42" s="32">
+      <c r="N42" s="33">
         <v>1.04</v>
       </c>
-      <c r="O42" s="32">
+      <c r="O42" s="33">
         <v>1.03</v>
       </c>
-      <c r="P42" s="32">
+      <c r="P42" s="33">
         <v>1.13</v>
       </c>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="31"/>
-      <c r="S42" s="31"/>
-      <c r="T42" s="31"/>
-      <c r="U42" s="31"/>
-      <c r="V42" s="31"/>
-      <c r="W42" s="31"/>
-      <c r="X42" s="31"/>
-      <c r="Y42" s="31"/>
+      <c r="Q42" s="32"/>
+      <c r="R42" s="32"/>
+      <c r="S42" s="32"/>
+      <c r="T42" s="32"/>
+      <c r="U42" s="32"/>
+      <c r="V42" s="32"/>
+      <c r="W42" s="32"/>
+      <c r="X42" s="32"/>
+      <c r="Y42" s="32"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="27" t="s">
-        <v>462</v>
-      </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="28"/>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
-      <c r="Q43" s="28"/>
-      <c r="R43" s="28"/>
-      <c r="S43" s="28"/>
-      <c r="T43" s="28"/>
-      <c r="U43" s="28"/>
-      <c r="V43" s="28"/>
-      <c r="W43" s="28"/>
-      <c r="X43" s="28"/>
-      <c r="Y43" s="28"/>
+      <c r="A43" s="28" t="s">
+        <v>463</v>
+      </c>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="29"/>
+      <c r="S43" s="29"/>
+      <c r="T43" s="29"/>
+      <c r="U43" s="29"/>
+      <c r="V43" s="29"/>
+      <c r="W43" s="29"/>
+      <c r="X43" s="29"/>
+      <c r="Y43" s="29"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="29" t="s">
-        <v>463</v>
-      </c>
-      <c r="B44" s="32">
+      <c r="A44" s="30" t="s">
+        <v>464</v>
+      </c>
+      <c r="B44" s="33">
         <v>0.19</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="33">
         <v>0.11</v>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="33">
         <v>0.11</v>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="33">
         <v>0.07</v>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="33">
         <v>0.15</v>
       </c>
-      <c r="G44" s="32">
+      <c r="G44" s="33">
         <v>0.11</v>
       </c>
-      <c r="H44" s="32">
+      <c r="H44" s="33">
         <v>0.08</v>
       </c>
-      <c r="I44" s="32">
+      <c r="I44" s="33">
         <v>0.11</v>
       </c>
-      <c r="J44" s="32">
+      <c r="J44" s="33">
         <v>0.19</v>
       </c>
-      <c r="K44" s="32">
+      <c r="K44" s="33">
         <v>0.37</v>
       </c>
-      <c r="L44" s="32">
+      <c r="L44" s="33">
         <v>0.18</v>
       </c>
-      <c r="M44" s="32">
+      <c r="M44" s="33">
         <v>0.15</v>
       </c>
-      <c r="N44" s="32">
+      <c r="N44" s="33">
         <v>0.21</v>
       </c>
-      <c r="O44" s="32">
+      <c r="O44" s="33">
         <v>0.18</v>
       </c>
-      <c r="P44" s="32">
+      <c r="P44" s="33">
         <v>0.21</v>
       </c>
-      <c r="Q44" s="32">
+      <c r="Q44" s="33">
         <v>0.46</v>
       </c>
-      <c r="R44" s="32">
+      <c r="R44" s="33">
         <v>0.54</v>
       </c>
-      <c r="S44" s="32">
+      <c r="S44" s="33">
         <v>0.24</v>
       </c>
-      <c r="T44" s="32">
+      <c r="T44" s="33">
         <v>0.3</v>
       </c>
-      <c r="U44" s="31"/>
-      <c r="V44" s="31"/>
-      <c r="W44" s="31"/>
-      <c r="X44" s="31"/>
-      <c r="Y44" s="31"/>
+      <c r="U44" s="32"/>
+      <c r="V44" s="32"/>
+      <c r="W44" s="32"/>
+      <c r="X44" s="32"/>
+      <c r="Y44" s="32"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="29" t="s">
-        <v>464</v>
-      </c>
-      <c r="B45" s="32">
+      <c r="A45" s="30" t="s">
+        <v>465</v>
+      </c>
+      <c r="B45" s="33">
         <v>0.12</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="33">
         <v>0.11</v>
       </c>
-      <c r="D45" s="32">
+      <c r="D45" s="33">
         <v>0.09</v>
       </c>
-      <c r="E45" s="32">
+      <c r="E45" s="33">
         <v>0.1</v>
       </c>
-      <c r="F45" s="32">
+      <c r="F45" s="33">
         <v>0.13</v>
       </c>
-      <c r="G45" s="32">
+      <c r="G45" s="33">
         <v>0.17</v>
       </c>
-      <c r="H45" s="32">
+      <c r="H45" s="33">
         <v>0.18</v>
       </c>
-      <c r="I45" s="32">
+      <c r="I45" s="33">
         <v>0.2</v>
       </c>
-      <c r="J45" s="32">
+      <c r="J45" s="33">
         <v>0.22</v>
       </c>
-      <c r="K45" s="32">
+      <c r="K45" s="33">
         <v>0.22</v>
       </c>
-      <c r="L45" s="32">
+      <c r="L45" s="33">
         <v>0.19</v>
       </c>
-      <c r="M45" s="32">
+      <c r="M45" s="33">
         <v>0.23</v>
       </c>
-      <c r="N45" s="32">
+      <c r="N45" s="33">
         <v>0.29</v>
       </c>
-      <c r="O45" s="32">
+      <c r="O45" s="33">
         <v>0.3</v>
       </c>
-      <c r="P45" s="32">
+      <c r="P45" s="33">
         <v>0.33</v>
       </c>
-      <c r="Q45" s="31"/>
-      <c r="R45" s="31"/>
-      <c r="S45" s="31"/>
-      <c r="T45" s="31"/>
-      <c r="U45" s="31"/>
-      <c r="V45" s="31"/>
-      <c r="W45" s="31"/>
-      <c r="X45" s="31"/>
-      <c r="Y45" s="31"/>
+      <c r="Q45" s="32"/>
+      <c r="R45" s="32"/>
+      <c r="S45" s="32"/>
+      <c r="T45" s="32"/>
+      <c r="U45" s="32"/>
+      <c r="V45" s="32"/>
+      <c r="W45" s="32"/>
+      <c r="X45" s="32"/>
+      <c r="Y45" s="32"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="27" t="s">
-        <v>465</v>
-      </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="28"/>
-      <c r="N46" s="28"/>
-      <c r="O46" s="28"/>
-      <c r="P46" s="28"/>
-      <c r="Q46" s="28"/>
-      <c r="R46" s="28"/>
-      <c r="S46" s="28"/>
-      <c r="T46" s="28"/>
-      <c r="U46" s="28"/>
-      <c r="V46" s="28"/>
-      <c r="W46" s="28"/>
-      <c r="X46" s="28"/>
-      <c r="Y46" s="28"/>
+      <c r="A46" s="28" t="s">
+        <v>466</v>
+      </c>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
+      <c r="U46" s="29"/>
+      <c r="V46" s="29"/>
+      <c r="W46" s="29"/>
+      <c r="X46" s="29"/>
+      <c r="Y46" s="29"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="29" t="s">
-        <v>466</v>
-      </c>
-      <c r="B47" s="32">
+      <c r="A47" s="30" t="s">
+        <v>467</v>
+      </c>
+      <c r="B47" s="33">
         <v>6.94</v>
       </c>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="32">
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="33">
         <v>2.06</v>
       </c>
-      <c r="G47" s="32">
+      <c r="G47" s="33">
         <v>2.29</v>
       </c>
-      <c r="H47" s="31"/>
-      <c r="I47" s="32">
+      <c r="H47" s="32"/>
+      <c r="I47" s="33">
         <v>5.93</v>
       </c>
-      <c r="J47" s="31"/>
-      <c r="K47" s="32">
+      <c r="J47" s="32"/>
+      <c r="K47" s="33">
         <v>14.44</v>
       </c>
-      <c r="L47" s="32">
+      <c r="L47" s="33">
         <v>1.76</v>
       </c>
-      <c r="M47" s="32">
+      <c r="M47" s="33">
         <v>1.92</v>
       </c>
-      <c r="N47" s="32">
+      <c r="N47" s="33">
         <v>3.04</v>
       </c>
-      <c r="O47" s="31"/>
-      <c r="P47" s="31"/>
-      <c r="Q47" s="31"/>
-      <c r="R47" s="31"/>
-      <c r="S47" s="31"/>
-      <c r="T47" s="31"/>
-      <c r="U47" s="31"/>
-      <c r="V47" s="31"/>
-      <c r="W47" s="31"/>
-      <c r="X47" s="31"/>
-      <c r="Y47" s="31"/>
+      <c r="O47" s="32"/>
+      <c r="P47" s="32"/>
+      <c r="Q47" s="32"/>
+      <c r="R47" s="32"/>
+      <c r="S47" s="32"/>
+      <c r="T47" s="32"/>
+      <c r="U47" s="32"/>
+      <c r="V47" s="32"/>
+      <c r="W47" s="32"/>
+      <c r="X47" s="32"/>
+      <c r="Y47" s="32"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="29" t="s">
-        <v>467</v>
-      </c>
-      <c r="B48" s="32">
+      <c r="A48" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="B48" s="33">
         <v>5.1</v>
       </c>
-      <c r="C48" s="32">
+      <c r="C48" s="33">
         <v>3.46</v>
       </c>
-      <c r="D48" s="32">
+      <c r="D48" s="33">
         <v>9.12</v>
       </c>
-      <c r="E48" s="32">
+      <c r="E48" s="33">
         <v>7.33</v>
       </c>
-      <c r="F48" s="30">
+      <c r="F48" s="31">
         <v>226.89</v>
       </c>
-      <c r="G48" s="30">
+      <c r="G48" s="31">
         <v>210.51</v>
       </c>
-      <c r="H48" s="32">
+      <c r="H48" s="33">
         <v>10.35</v>
       </c>
-      <c r="I48" s="32">
+      <c r="I48" s="33">
         <v>5.44</v>
       </c>
-      <c r="J48" s="32">
+      <c r="J48" s="33">
         <v>4.7</v>
       </c>
-      <c r="K48" s="32">
+      <c r="K48" s="33">
         <v>4.7</v>
       </c>
-      <c r="L48" s="32">
+      <c r="L48" s="33">
         <v>4.69</v>
       </c>
-      <c r="M48" s="32">
+      <c r="M48" s="33">
         <v>18.71</v>
       </c>
-      <c r="N48" s="31"/>
-      <c r="O48" s="31"/>
-      <c r="P48" s="31"/>
-      <c r="Q48" s="31"/>
-      <c r="R48" s="31"/>
-      <c r="S48" s="31"/>
-      <c r="T48" s="31"/>
-      <c r="U48" s="31"/>
-      <c r="V48" s="31"/>
-      <c r="W48" s="31"/>
-      <c r="X48" s="31"/>
-      <c r="Y48" s="31"/>
+      <c r="N48" s="32"/>
+      <c r="O48" s="32"/>
+      <c r="P48" s="32"/>
+      <c r="Q48" s="32"/>
+      <c r="R48" s="32"/>
+      <c r="S48" s="32"/>
+      <c r="T48" s="32"/>
+      <c r="U48" s="32"/>
+      <c r="V48" s="32"/>
+      <c r="W48" s="32"/>
+      <c r="X48" s="32"/>
+      <c r="Y48" s="32"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="27" t="s">
-        <v>468</v>
-      </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28"/>
-      <c r="M49" s="28"/>
-      <c r="N49" s="28"/>
-      <c r="O49" s="28"/>
-      <c r="P49" s="28"/>
-      <c r="Q49" s="28"/>
-      <c r="R49" s="28"/>
-      <c r="S49" s="28"/>
-      <c r="T49" s="28"/>
-      <c r="U49" s="28"/>
-      <c r="V49" s="28"/>
-      <c r="W49" s="28"/>
-      <c r="X49" s="28"/>
-      <c r="Y49" s="28"/>
+      <c r="A49" s="28" t="s">
+        <v>469</v>
+      </c>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="29"/>
+      <c r="O49" s="29"/>
+      <c r="P49" s="29"/>
+      <c r="Q49" s="29"/>
+      <c r="R49" s="29"/>
+      <c r="S49" s="29"/>
+      <c r="T49" s="29"/>
+      <c r="U49" s="29"/>
+      <c r="V49" s="29"/>
+      <c r="W49" s="29"/>
+      <c r="X49" s="29"/>
+      <c r="Y49" s="29"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="29" t="s">
-        <v>469</v>
-      </c>
-      <c r="B50" s="32">
+      <c r="A50" s="30" t="s">
+        <v>470</v>
+      </c>
+      <c r="B50" s="33">
         <v>6.45</v>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="33">
         <v>7.52</v>
       </c>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="31"/>
-      <c r="G50" s="31"/>
-      <c r="H50" s="31"/>
-      <c r="I50" s="31"/>
-      <c r="J50" s="32">
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="33">
         <v>20.36</v>
       </c>
-      <c r="K50" s="32">
+      <c r="K50" s="33">
         <v>17.5</v>
       </c>
-      <c r="L50" s="32">
+      <c r="L50" s="33">
         <v>7.57</v>
       </c>
-      <c r="M50" s="32">
+      <c r="M50" s="33">
         <v>5.43</v>
       </c>
-      <c r="N50" s="32">
+      <c r="N50" s="33">
         <v>6.73</v>
       </c>
-      <c r="O50" s="32">
+      <c r="O50" s="33">
         <v>21.53</v>
       </c>
-      <c r="P50" s="32">
+      <c r="P50" s="33">
         <v>15.59</v>
       </c>
-      <c r="Q50" s="32">
+      <c r="Q50" s="33">
         <v>25.91</v>
       </c>
-      <c r="R50" s="32">
+      <c r="R50" s="33">
         <v>32.03</v>
       </c>
-      <c r="S50" s="32">
+      <c r="S50" s="33">
         <v>6.88</v>
       </c>
-      <c r="T50" s="32">
+      <c r="T50" s="33">
         <v>17.88</v>
       </c>
-      <c r="U50" s="31"/>
-      <c r="V50" s="31"/>
-      <c r="W50" s="31"/>
-      <c r="X50" s="31"/>
-      <c r="Y50" s="31"/>
+      <c r="U50" s="32"/>
+      <c r="V50" s="32"/>
+      <c r="W50" s="32"/>
+      <c r="X50" s="32"/>
+      <c r="Y50" s="32"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="29" t="s">
-        <v>470</v>
-      </c>
-      <c r="B51" s="31"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="31"/>
-      <c r="G51" s="31"/>
-      <c r="H51" s="31"/>
-      <c r="I51" s="32">
+      <c r="A51" s="30" t="s">
+        <v>471</v>
+      </c>
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="33">
         <v>18.69</v>
       </c>
-      <c r="J51" s="32">
+      <c r="J51" s="33">
         <v>9.76</v>
       </c>
-      <c r="K51" s="32">
+      <c r="K51" s="33">
         <v>9.54</v>
       </c>
-      <c r="L51" s="32">
+      <c r="L51" s="33">
         <v>8.83</v>
       </c>
-      <c r="M51" s="32">
+      <c r="M51" s="33">
         <v>11.63</v>
       </c>
-      <c r="N51" s="32">
+      <c r="N51" s="33">
         <v>16.44</v>
       </c>
-      <c r="O51" s="32">
+      <c r="O51" s="33">
         <v>17.19</v>
       </c>
-      <c r="P51" s="32">
+      <c r="P51" s="33">
         <v>16.88</v>
       </c>
-      <c r="Q51" s="31"/>
-      <c r="R51" s="31"/>
-      <c r="S51" s="31"/>
-      <c r="T51" s="31"/>
-      <c r="U51" s="31"/>
-      <c r="V51" s="31"/>
-      <c r="W51" s="31"/>
-      <c r="X51" s="31"/>
-      <c r="Y51" s="31"/>
+      <c r="Q51" s="32"/>
+      <c r="R51" s="32"/>
+      <c r="S51" s="32"/>
+      <c r="T51" s="32"/>
+      <c r="U51" s="32"/>
+      <c r="V51" s="32"/>
+      <c r="W51" s="32"/>
+      <c r="X51" s="32"/>
+      <c r="Y51" s="32"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="27" t="s">
-        <v>471</v>
-      </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="28"/>
-      <c r="O52" s="28"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="28"/>
-      <c r="R52" s="28"/>
-      <c r="S52" s="28"/>
-      <c r="T52" s="28"/>
-      <c r="U52" s="28"/>
-      <c r="V52" s="28"/>
-      <c r="W52" s="28"/>
-      <c r="X52" s="28"/>
-      <c r="Y52" s="28"/>
+      <c r="A52" s="28" t="s">
+        <v>472</v>
+      </c>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+      <c r="L52" s="29"/>
+      <c r="M52" s="29"/>
+      <c r="N52" s="29"/>
+      <c r="O52" s="29"/>
+      <c r="P52" s="29"/>
+      <c r="Q52" s="29"/>
+      <c r="R52" s="29"/>
+      <c r="S52" s="29"/>
+      <c r="T52" s="29"/>
+      <c r="U52" s="29"/>
+      <c r="V52" s="29"/>
+      <c r="W52" s="29"/>
+      <c r="X52" s="29"/>
+      <c r="Y52" s="29"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="29" t="s">
-        <v>472</v>
-      </c>
-      <c r="B53" s="32">
+      <c r="A53" s="30" t="s">
+        <v>473</v>
+      </c>
+      <c r="B53" s="33">
         <v>10.36</v>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="33">
         <v>26.02</v>
       </c>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="32">
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="33">
         <v>75.55</v>
       </c>
-      <c r="K53" s="32">
+      <c r="K53" s="33">
         <v>36.87</v>
       </c>
-      <c r="L53" s="32">
+      <c r="L53" s="33">
         <v>12.47</v>
       </c>
-      <c r="M53" s="32">
+      <c r="M53" s="33">
         <v>8.52</v>
       </c>
-      <c r="N53" s="32">
+      <c r="N53" s="33">
         <v>9.55</v>
       </c>
-      <c r="O53" s="30">
+      <c r="O53" s="31">
         <v>144.63</v>
       </c>
-      <c r="P53" s="32">
+      <c r="P53" s="33">
         <v>24.34</v>
       </c>
-      <c r="Q53" s="32">
+      <c r="Q53" s="33">
         <v>35.22</v>
       </c>
-      <c r="R53" s="32">
+      <c r="R53" s="33">
         <v>73.52</v>
       </c>
-      <c r="S53" s="32">
+      <c r="S53" s="33">
         <v>8.07</v>
       </c>
-      <c r="T53" s="32">
+      <c r="T53" s="33">
         <v>23.79</v>
       </c>
-      <c r="U53" s="31"/>
-      <c r="V53" s="31"/>
-      <c r="W53" s="31"/>
-      <c r="X53" s="31"/>
-      <c r="Y53" s="31"/>
+      <c r="U53" s="32"/>
+      <c r="V53" s="32"/>
+      <c r="W53" s="32"/>
+      <c r="X53" s="32"/>
+      <c r="Y53" s="32"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="29" t="s">
-        <v>473</v>
-      </c>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="31"/>
-      <c r="G54" s="31"/>
-      <c r="H54" s="31"/>
-      <c r="I54" s="30">
+      <c r="A54" s="30" t="s">
+        <v>474</v>
+      </c>
+      <c r="B54" s="32"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="31">
         <v>100.89</v>
       </c>
-      <c r="J54" s="32">
+      <c r="J54" s="33">
         <v>16.66</v>
       </c>
-      <c r="K54" s="32">
+      <c r="K54" s="33">
         <v>16.26</v>
       </c>
-      <c r="L54" s="32">
+      <c r="L54" s="33">
         <v>14.38</v>
       </c>
-      <c r="M54" s="32">
+      <c r="M54" s="33">
         <v>18.35</v>
       </c>
-      <c r="N54" s="32">
+      <c r="N54" s="33">
         <v>27.1</v>
       </c>
-      <c r="O54" s="32">
+      <c r="O54" s="33">
         <v>26.27</v>
       </c>
-      <c r="P54" s="32">
+      <c r="P54" s="33">
         <v>23.3</v>
       </c>
-      <c r="Q54" s="31"/>
-      <c r="R54" s="31"/>
-      <c r="S54" s="31"/>
-      <c r="T54" s="31"/>
-      <c r="U54" s="31"/>
-      <c r="V54" s="31"/>
-      <c r="W54" s="31"/>
-      <c r="X54" s="31"/>
-      <c r="Y54" s="31"/>
+      <c r="Q54" s="32"/>
+      <c r="R54" s="32"/>
+      <c r="S54" s="32"/>
+      <c r="T54" s="32"/>
+      <c r="U54" s="32"/>
+      <c r="V54" s="32"/>
+      <c r="W54" s="32"/>
+      <c r="X54" s="32"/>
+      <c r="Y54" s="32"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="27" t="s">
-        <v>474</v>
-      </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="28"/>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
-      <c r="J55" s="28"/>
-      <c r="K55" s="28"/>
-      <c r="L55" s="28"/>
-      <c r="M55" s="28"/>
-      <c r="N55" s="28"/>
-      <c r="O55" s="28"/>
-      <c r="P55" s="28"/>
-      <c r="Q55" s="28"/>
-      <c r="R55" s="28"/>
-      <c r="S55" s="28"/>
-      <c r="T55" s="28"/>
-      <c r="U55" s="28"/>
-      <c r="V55" s="28"/>
-      <c r="W55" s="28"/>
-      <c r="X55" s="28"/>
-      <c r="Y55" s="28"/>
+      <c r="A55" s="28" t="s">
+        <v>475</v>
+      </c>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="29"/>
+      <c r="E55" s="29"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="29"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
+      <c r="L55" s="29"/>
+      <c r="M55" s="29"/>
+      <c r="N55" s="29"/>
+      <c r="O55" s="29"/>
+      <c r="P55" s="29"/>
+      <c r="Q55" s="29"/>
+      <c r="R55" s="29"/>
+      <c r="S55" s="29"/>
+      <c r="T55" s="29"/>
+      <c r="U55" s="29"/>
+      <c r="V55" s="29"/>
+      <c r="W55" s="29"/>
+      <c r="X55" s="29"/>
+      <c r="Y55" s="29"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="29" t="s">
-        <v>475</v>
-      </c>
-      <c r="B56" s="31"/>
-      <c r="C56" s="32">
+      <c r="A56" s="30" t="s">
+        <v>476</v>
+      </c>
+      <c r="B56" s="32"/>
+      <c r="C56" s="33">
         <v>12.07</v>
       </c>
-      <c r="D56" s="31"/>
-      <c r="E56" s="32">
+      <c r="D56" s="32"/>
+      <c r="E56" s="33">
         <v>0.52</v>
       </c>
-      <c r="F56" s="31"/>
-      <c r="G56" s="31"/>
-      <c r="H56" s="31"/>
-      <c r="I56" s="31"/>
-      <c r="J56" s="30">
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="31">
         <v>110.77</v>
       </c>
-      <c r="K56" s="32">
+      <c r="K56" s="33">
         <v>20.25</v>
       </c>
-      <c r="L56" s="32">
+      <c r="L56" s="33">
         <v>9.49</v>
       </c>
-      <c r="M56" s="32">
+      <c r="M56" s="33">
         <v>9.74</v>
       </c>
-      <c r="N56" s="32">
+      <c r="N56" s="33">
         <v>10.08</v>
       </c>
-      <c r="O56" s="30">
+      <c r="O56" s="31">
         <v>200.61</v>
       </c>
-      <c r="P56" s="32">
+      <c r="P56" s="33">
         <v>24.34</v>
       </c>
-      <c r="Q56" s="32">
+      <c r="Q56" s="33">
         <v>35.22</v>
       </c>
-      <c r="R56" s="32">
+      <c r="R56" s="33">
         <v>73.47</v>
       </c>
-      <c r="S56" s="32">
+      <c r="S56" s="33">
         <v>8.07</v>
       </c>
-      <c r="T56" s="32">
+      <c r="T56" s="33">
         <v>23.79</v>
       </c>
-      <c r="U56" s="31"/>
-      <c r="V56" s="31"/>
-      <c r="W56" s="31"/>
-      <c r="X56" s="31"/>
-      <c r="Y56" s="31"/>
+      <c r="U56" s="32"/>
+      <c r="V56" s="32"/>
+      <c r="W56" s="32"/>
+      <c r="X56" s="32"/>
+      <c r="Y56" s="32"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="29" t="s">
-        <v>476</v>
-      </c>
-      <c r="B57" s="32">
+      <c r="A57" s="30" t="s">
+        <v>477</v>
+      </c>
+      <c r="B57" s="33">
         <v>0.74</v>
       </c>
-      <c r="C57" s="32">
+      <c r="C57" s="33">
         <v>0.81</v>
       </c>
-      <c r="D57" s="32">
+      <c r="D57" s="33">
         <v>0.84</v>
       </c>
-      <c r="E57" s="32">
+      <c r="E57" s="33">
         <v>0.7</v>
       </c>
-      <c r="F57" s="32">
+      <c r="F57" s="33">
         <v>0.78</v>
       </c>
-      <c r="G57" s="32">
+      <c r="G57" s="33">
         <v>0.92</v>
       </c>
-      <c r="H57" s="32">
+      <c r="H57" s="33">
         <v>0.89</v>
       </c>
-      <c r="I57" s="32">
+      <c r="I57" s="33">
         <v>0.83</v>
       </c>
-      <c r="J57" s="32">
+      <c r="J57" s="33">
         <v>0.87</v>
       </c>
-      <c r="K57" s="32">
+      <c r="K57" s="33">
         <v>0.84</v>
       </c>
-      <c r="L57" s="32">
+      <c r="L57" s="33">
         <v>0.74</v>
       </c>
-      <c r="M57" s="32">
+      <c r="M57" s="33">
         <v>0.87</v>
       </c>
-      <c r="N57" s="32">
+      <c r="N57" s="33">
         <v>1.02</v>
       </c>
-      <c r="O57" s="32">
+      <c r="O57" s="33">
         <v>1.02</v>
       </c>
-      <c r="P57" s="32">
+      <c r="P57" s="33">
         <v>1.11</v>
       </c>
-      <c r="Q57" s="31"/>
-      <c r="R57" s="31"/>
-      <c r="S57" s="31"/>
-      <c r="T57" s="31"/>
-      <c r="U57" s="31"/>
-      <c r="V57" s="31"/>
-      <c r="W57" s="31"/>
-      <c r="X57" s="31"/>
-      <c r="Y57" s="31"/>
+      <c r="Q57" s="32"/>
+      <c r="R57" s="32"/>
+      <c r="S57" s="32"/>
+      <c r="T57" s="32"/>
+      <c r="U57" s="32"/>
+      <c r="V57" s="32"/>
+      <c r="W57" s="32"/>
+      <c r="X57" s="32"/>
+      <c r="Y57" s="32"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="27" t="s">
-        <v>477</v>
-      </c>
-      <c r="B58" s="28"/>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="28"/>
-      <c r="J58" s="28"/>
-      <c r="K58" s="28"/>
-      <c r="L58" s="28"/>
-      <c r="M58" s="28"/>
-      <c r="N58" s="28"/>
-      <c r="O58" s="28"/>
-      <c r="P58" s="28"/>
-      <c r="Q58" s="28"/>
-      <c r="R58" s="28"/>
-      <c r="S58" s="28"/>
-      <c r="T58" s="28"/>
-      <c r="U58" s="28"/>
-      <c r="V58" s="28"/>
-      <c r="W58" s="28"/>
-      <c r="X58" s="28"/>
-      <c r="Y58" s="28"/>
+      <c r="A58" s="28" t="s">
+        <v>478</v>
+      </c>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="29"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="29"/>
+      <c r="L58" s="29"/>
+      <c r="M58" s="29"/>
+      <c r="N58" s="29"/>
+      <c r="O58" s="29"/>
+      <c r="P58" s="29"/>
+      <c r="Q58" s="29"/>
+      <c r="R58" s="29"/>
+      <c r="S58" s="29"/>
+      <c r="T58" s="29"/>
+      <c r="U58" s="29"/>
+      <c r="V58" s="29"/>
+      <c r="W58" s="29"/>
+      <c r="X58" s="29"/>
+      <c r="Y58" s="29"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="29" t="s">
-        <v>478</v>
-      </c>
-      <c r="B59" s="32">
+      <c r="A59" s="30" t="s">
+        <v>479</v>
+      </c>
+      <c r="B59" s="33">
         <v>0.08</v>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="33">
         <v>0.22</v>
       </c>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="31"/>
-      <c r="H59" s="31"/>
-      <c r="I59" s="31"/>
-      <c r="J59" s="35">
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="36">
         <v>-1.12</v>
       </c>
-      <c r="K59" s="35">
+      <c r="K59" s="36">
         <v>-0.9</v>
       </c>
-      <c r="L59" s="35">
+      <c r="L59" s="36">
         <v>-1.29</v>
       </c>
-      <c r="M59" s="35">
+      <c r="M59" s="36">
         <v>-0.39</v>
       </c>
-      <c r="N59" s="32">
+      <c r="N59" s="33">
         <v>0.01</v>
       </c>
-      <c r="O59" s="35">
+      <c r="O59" s="36">
         <v>-1.68</v>
       </c>
-      <c r="P59" s="35">
+      <c r="P59" s="36">
         <v>-1.92</v>
       </c>
-      <c r="Q59" s="32">
+      <c r="Q59" s="33">
         <v>0.26</v>
       </c>
-      <c r="R59" s="35">
+      <c r="R59" s="36">
         <v>-0.9</v>
       </c>
-      <c r="S59" s="32">
+      <c r="S59" s="33">
         <v>0.08</v>
       </c>
-      <c r="T59" s="35">
+      <c r="T59" s="36">
         <v>-0.38</v>
       </c>
-      <c r="U59" s="31"/>
-      <c r="V59" s="31"/>
-      <c r="W59" s="31"/>
-      <c r="X59" s="31"/>
-      <c r="Y59" s="31"/>
+      <c r="U59" s="32"/>
+      <c r="V59" s="32"/>
+      <c r="W59" s="32"/>
+      <c r="X59" s="32"/>
+      <c r="Y59" s="32"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="29" t="s">
-        <v>479</v>
-      </c>
-      <c r="B60" s="31"/>
-      <c r="C60" s="31"/>
-      <c r="D60" s="31"/>
-      <c r="E60" s="31"/>
-      <c r="F60" s="31"/>
-      <c r="G60" s="31"/>
-      <c r="H60" s="31"/>
-      <c r="I60" s="31"/>
-      <c r="J60" s="32">
+      <c r="A60" s="30" t="s">
+        <v>480</v>
+      </c>
+      <c r="B60" s="32"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="32"/>
+      <c r="I60" s="32"/>
+      <c r="J60" s="33">
         <v>0.81</v>
       </c>
-      <c r="K60" s="32">
+      <c r="K60" s="33">
         <v>10.2</v>
       </c>
-      <c r="L60" s="32">
+      <c r="L60" s="33">
         <v>1.47</v>
       </c>
-      <c r="M60" s="32">
+      <c r="M60" s="33">
         <v>0.56</v>
       </c>
-      <c r="N60" s="36">
+      <c r="N60" s="37">
         <v>-101.64</v>
       </c>
-      <c r="O60" s="35">
+      <c r="O60" s="36">
         <v>-0.73</v>
       </c>
-      <c r="P60" s="35">
+      <c r="P60" s="36">
         <v>-1.08</v>
       </c>
-      <c r="Q60" s="31"/>
-      <c r="R60" s="31"/>
-      <c r="S60" s="31"/>
-      <c r="T60" s="31"/>
-      <c r="U60" s="31"/>
-      <c r="V60" s="31"/>
-      <c r="W60" s="31"/>
-      <c r="X60" s="31"/>
-      <c r="Y60" s="31"/>
+      <c r="Q60" s="32"/>
+      <c r="R60" s="32"/>
+      <c r="S60" s="32"/>
+      <c r="T60" s="32"/>
+      <c r="U60" s="32"/>
+      <c r="V60" s="32"/>
+      <c r="W60" s="32"/>
+      <c r="X60" s="32"/>
+      <c r="Y60" s="32"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="27" t="s">
-        <v>480</v>
-      </c>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="28"/>
-      <c r="J61" s="28"/>
-      <c r="K61" s="28"/>
-      <c r="L61" s="28"/>
-      <c r="M61" s="28"/>
-      <c r="N61" s="28"/>
-      <c r="O61" s="28"/>
-      <c r="P61" s="28"/>
-      <c r="Q61" s="28"/>
-      <c r="R61" s="28"/>
-      <c r="S61" s="28"/>
-      <c r="T61" s="28"/>
-      <c r="U61" s="28"/>
-      <c r="V61" s="28"/>
-      <c r="W61" s="28"/>
-      <c r="X61" s="28"/>
-      <c r="Y61" s="28"/>
+      <c r="A61" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="29"/>
+      <c r="E61" s="29"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="29"/>
+      <c r="H61" s="29"/>
+      <c r="I61" s="29"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="29"/>
+      <c r="L61" s="29"/>
+      <c r="M61" s="29"/>
+      <c r="N61" s="29"/>
+      <c r="O61" s="29"/>
+      <c r="P61" s="29"/>
+      <c r="Q61" s="29"/>
+      <c r="R61" s="29"/>
+      <c r="S61" s="29"/>
+      <c r="T61" s="29"/>
+      <c r="U61" s="29"/>
+      <c r="V61" s="29"/>
+      <c r="W61" s="29"/>
+      <c r="X61" s="29"/>
+      <c r="Y61" s="29"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="29" t="s">
-        <v>481</v>
-      </c>
-      <c r="B62" s="32">
+      <c r="A62" s="30" t="s">
+        <v>482</v>
+      </c>
+      <c r="B62" s="33">
         <v>0.18</v>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="33">
         <v>0.24</v>
       </c>
-      <c r="D62" s="32">
+      <c r="D62" s="33">
         <v>0.28</v>
       </c>
-      <c r="E62" s="32">
+      <c r="E62" s="33">
         <v>0.19</v>
       </c>
-      <c r="F62" s="32">
+      <c r="F62" s="33">
         <v>0.33</v>
       </c>
-      <c r="G62" s="32">
+      <c r="G62" s="33">
         <v>0.45</v>
       </c>
-      <c r="H62" s="32">
+      <c r="H62" s="33">
         <v>0.47</v>
       </c>
-      <c r="I62" s="32">
+      <c r="I62" s="33">
         <v>0.4</v>
       </c>
-      <c r="J62" s="32">
+      <c r="J62" s="33">
         <v>0.46</v>
       </c>
-      <c r="K62" s="32">
+      <c r="K62" s="33">
         <v>0.65</v>
       </c>
-      <c r="L62" s="32">
+      <c r="L62" s="33">
         <v>0.58</v>
       </c>
-      <c r="M62" s="32">
+      <c r="M62" s="33">
         <v>0.45</v>
       </c>
-      <c r="N62" s="32">
+      <c r="N62" s="33">
         <v>0.54</v>
       </c>
-      <c r="O62" s="32">
+      <c r="O62" s="33">
         <v>0.68</v>
       </c>
-      <c r="P62" s="32">
+      <c r="P62" s="33">
         <v>0.62</v>
       </c>
-      <c r="Q62" s="32">
+      <c r="Q62" s="33">
         <v>0.96</v>
       </c>
-      <c r="R62" s="32">
+      <c r="R62" s="33">
         <v>1.02</v>
       </c>
-      <c r="S62" s="32">
+      <c r="S62" s="33">
         <v>0.56</v>
       </c>
-      <c r="T62" s="32">
+      <c r="T62" s="33">
         <v>0.41</v>
       </c>
-      <c r="U62" s="31"/>
-      <c r="V62" s="31"/>
-      <c r="W62" s="31"/>
-      <c r="X62" s="31"/>
-      <c r="Y62" s="31"/>
+      <c r="U62" s="32"/>
+      <c r="V62" s="32"/>
+      <c r="W62" s="32"/>
+      <c r="X62" s="32"/>
+      <c r="Y62" s="32"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="29" t="s">
-        <v>482</v>
-      </c>
-      <c r="B63" s="32">
+      <c r="A63" s="30" t="s">
+        <v>483</v>
+      </c>
+      <c r="B63" s="33">
         <v>0.25</v>
       </c>
-      <c r="C63" s="32">
+      <c r="C63" s="33">
         <v>0.31</v>
       </c>
-      <c r="D63" s="32">
+      <c r="D63" s="33">
         <v>0.36</v>
       </c>
-      <c r="E63" s="32">
+      <c r="E63" s="33">
         <v>0.38</v>
       </c>
-      <c r="F63" s="32">
+      <c r="F63" s="33">
         <v>0.43</v>
       </c>
-      <c r="G63" s="32">
+      <c r="G63" s="33">
         <v>0.48</v>
       </c>
-      <c r="H63" s="32">
+      <c r="H63" s="33">
         <v>0.5</v>
       </c>
-      <c r="I63" s="32">
+      <c r="I63" s="33">
         <v>0.5</v>
       </c>
-      <c r="J63" s="32">
+      <c r="J63" s="33">
         <v>0.53</v>
       </c>
-      <c r="K63" s="32">
+      <c r="K63" s="33">
         <v>0.58</v>
       </c>
-      <c r="L63" s="32">
+      <c r="L63" s="33">
         <v>0.57</v>
       </c>
-      <c r="M63" s="32">
+      <c r="M63" s="33">
         <v>0.63</v>
       </c>
-      <c r="N63" s="32">
+      <c r="N63" s="33">
         <v>0.73</v>
       </c>
-      <c r="O63" s="32">
+      <c r="O63" s="33">
         <v>0.74</v>
       </c>
-      <c r="P63" s="32">
+      <c r="P63" s="33">
         <v>0.69</v>
       </c>
-      <c r="Q63" s="31"/>
-      <c r="R63" s="31"/>
-      <c r="S63" s="31"/>
-      <c r="T63" s="31"/>
-      <c r="U63" s="31"/>
-      <c r="V63" s="31"/>
-      <c r="W63" s="31"/>
-      <c r="X63" s="31"/>
-      <c r="Y63" s="31"/>
+      <c r="Q63" s="32"/>
+      <c r="R63" s="32"/>
+      <c r="S63" s="32"/>
+      <c r="T63" s="32"/>
+      <c r="U63" s="32"/>
+      <c r="V63" s="32"/>
+      <c r="W63" s="32"/>
+      <c r="X63" s="32"/>
+      <c r="Y63" s="32"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="27" t="s">
-        <v>483</v>
-      </c>
-      <c r="B64" s="28"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="28"/>
-      <c r="E64" s="28"/>
-      <c r="F64" s="28"/>
-      <c r="G64" s="28"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="28"/>
-      <c r="J64" s="28"/>
-      <c r="K64" s="28"/>
-      <c r="L64" s="28"/>
-      <c r="M64" s="28"/>
-      <c r="N64" s="28"/>
-      <c r="O64" s="28"/>
-      <c r="P64" s="28"/>
-      <c r="Q64" s="28"/>
-      <c r="R64" s="28"/>
-      <c r="S64" s="28"/>
-      <c r="T64" s="28"/>
-      <c r="U64" s="28"/>
-      <c r="V64" s="28"/>
-      <c r="W64" s="28"/>
-      <c r="X64" s="28"/>
-      <c r="Y64" s="28"/>
+      <c r="A64" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
+      <c r="D64" s="29"/>
+      <c r="E64" s="29"/>
+      <c r="F64" s="29"/>
+      <c r="G64" s="29"/>
+      <c r="H64" s="29"/>
+      <c r="I64" s="29"/>
+      <c r="J64" s="29"/>
+      <c r="K64" s="29"/>
+      <c r="L64" s="29"/>
+      <c r="M64" s="29"/>
+      <c r="N64" s="29"/>
+      <c r="O64" s="29"/>
+      <c r="P64" s="29"/>
+      <c r="Q64" s="29"/>
+      <c r="R64" s="29"/>
+      <c r="S64" s="29"/>
+      <c r="T64" s="29"/>
+      <c r="U64" s="29"/>
+      <c r="V64" s="29"/>
+      <c r="W64" s="29"/>
+      <c r="X64" s="29"/>
+      <c r="Y64" s="29"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="29" t="s">
-        <v>484</v>
-      </c>
-      <c r="B65" s="32">
+      <c r="A65" s="30" t="s">
+        <v>485</v>
+      </c>
+      <c r="B65" s="33">
         <v>11.66</v>
       </c>
-      <c r="C65" s="32">
+      <c r="C65" s="33">
         <v>10.75</v>
       </c>
-      <c r="D65" s="32">
+      <c r="D65" s="33">
         <v>24.34</v>
       </c>
-      <c r="E65" s="32">
+      <c r="E65" s="33">
         <v>1.48</v>
       </c>
-      <c r="F65" s="30">
+      <c r="F65" s="31">
         <v>206.94</v>
       </c>
-      <c r="G65" s="32">
+      <c r="G65" s="33">
         <v>16.4</v>
       </c>
-      <c r="H65" s="31"/>
-      <c r="I65" s="31"/>
-      <c r="J65" s="32">
+      <c r="H65" s="32"/>
+      <c r="I65" s="32"/>
+      <c r="J65" s="33">
         <v>14.38</v>
       </c>
-      <c r="K65" s="32">
+      <c r="K65" s="33">
         <v>16.58</v>
       </c>
-      <c r="L65" s="32">
+      <c r="L65" s="33">
         <v>15.87</v>
       </c>
-      <c r="M65" s="32">
+      <c r="M65" s="33">
         <v>14.34</v>
       </c>
-      <c r="N65" s="32">
+      <c r="N65" s="33">
         <v>12.95</v>
       </c>
-      <c r="O65" s="32">
+      <c r="O65" s="33">
         <v>45.99</v>
       </c>
-      <c r="P65" s="32">
+      <c r="P65" s="33">
         <v>22.47</v>
       </c>
-      <c r="Q65" s="32">
+      <c r="Q65" s="33">
         <v>28.71</v>
       </c>
-      <c r="R65" s="32">
+      <c r="R65" s="33">
         <v>27.79</v>
       </c>
-      <c r="S65" s="32">
+      <c r="S65" s="33">
         <v>8.35</v>
       </c>
-      <c r="T65" s="32">
+      <c r="T65" s="33">
         <v>13.58</v>
       </c>
-      <c r="U65" s="31"/>
-      <c r="V65" s="31"/>
-      <c r="W65" s="31"/>
-      <c r="X65" s="31"/>
-      <c r="Y65" s="31"/>
+      <c r="U65" s="32"/>
+      <c r="V65" s="32"/>
+      <c r="W65" s="32"/>
+      <c r="X65" s="32"/>
+      <c r="Y65" s="32"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="29" t="s">
-        <v>485</v>
-      </c>
-      <c r="B66" s="32">
+      <c r="A66" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B66" s="33">
         <v>38.48</v>
       </c>
-      <c r="C66" s="32">
+      <c r="C66" s="33">
         <v>31.06</v>
       </c>
-      <c r="D66" s="32">
+      <c r="D66" s="33">
         <v>72.43</v>
       </c>
-      <c r="E66" s="32">
+      <c r="E66" s="33">
         <v>18.48</v>
       </c>
-      <c r="F66" s="32">
+      <c r="F66" s="33">
         <v>62.36</v>
       </c>
-      <c r="G66" s="32">
+      <c r="G66" s="33">
         <v>35.73</v>
       </c>
-      <c r="H66" s="32">
+      <c r="H66" s="33">
         <v>35.67</v>
       </c>
-      <c r="I66" s="32">
+      <c r="I66" s="33">
         <v>24.25</v>
       </c>
-      <c r="J66" s="32">
+      <c r="J66" s="33">
         <v>14.89</v>
       </c>
-      <c r="K66" s="32">
+      <c r="K66" s="33">
         <v>17.49</v>
       </c>
-      <c r="L66" s="32">
+      <c r="L66" s="33">
         <v>18.68</v>
       </c>
-      <c r="M66" s="32">
+      <c r="M66" s="33">
         <v>21.2</v>
       </c>
-      <c r="N66" s="32">
+      <c r="N66" s="33">
         <v>23.99</v>
       </c>
-      <c r="O66" s="32">
+      <c r="O66" s="33">
         <v>21.34</v>
       </c>
-      <c r="P66" s="32">
+      <c r="P66" s="33">
         <v>17.78</v>
       </c>
-      <c r="Q66" s="31"/>
-      <c r="R66" s="31"/>
-      <c r="S66" s="31"/>
-      <c r="T66" s="31"/>
-      <c r="U66" s="31"/>
-      <c r="V66" s="31"/>
-      <c r="W66" s="31"/>
-      <c r="X66" s="31"/>
-      <c r="Y66" s="31"/>
+      <c r="Q66" s="32"/>
+      <c r="R66" s="32"/>
+      <c r="S66" s="32"/>
+      <c r="T66" s="32"/>
+      <c r="U66" s="32"/>
+      <c r="V66" s="32"/>
+      <c r="W66" s="32"/>
+      <c r="X66" s="32"/>
+      <c r="Y66" s="32"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="27" t="s">
-        <v>486</v>
-      </c>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="28"/>
-      <c r="J67" s="28"/>
-      <c r="K67" s="28"/>
-      <c r="L67" s="28"/>
-      <c r="M67" s="28"/>
-      <c r="N67" s="28"/>
-      <c r="O67" s="28"/>
-      <c r="P67" s="28"/>
-      <c r="Q67" s="28"/>
-      <c r="R67" s="28"/>
-      <c r="S67" s="28"/>
-      <c r="T67" s="28"/>
-      <c r="U67" s="28"/>
-      <c r="V67" s="28"/>
-      <c r="W67" s="28"/>
-      <c r="X67" s="28"/>
-      <c r="Y67" s="28"/>
+      <c r="A67" s="28" t="s">
+        <v>487</v>
+      </c>
+      <c r="B67" s="29"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="29"/>
+      <c r="E67" s="29"/>
+      <c r="F67" s="29"/>
+      <c r="G67" s="29"/>
+      <c r="H67" s="29"/>
+      <c r="I67" s="29"/>
+      <c r="J67" s="29"/>
+      <c r="K67" s="29"/>
+      <c r="L67" s="29"/>
+      <c r="M67" s="29"/>
+      <c r="N67" s="29"/>
+      <c r="O67" s="29"/>
+      <c r="P67" s="29"/>
+      <c r="Q67" s="29"/>
+      <c r="R67" s="29"/>
+      <c r="S67" s="29"/>
+      <c r="T67" s="29"/>
+      <c r="U67" s="29"/>
+      <c r="V67" s="29"/>
+      <c r="W67" s="29"/>
+      <c r="X67" s="29"/>
+      <c r="Y67" s="29"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="29" t="s">
-        <v>487</v>
-      </c>
-      <c r="B68" s="32">
+      <c r="A68" s="30" t="s">
+        <v>488</v>
+      </c>
+      <c r="B68" s="33">
         <v>5.09</v>
       </c>
-      <c r="C68" s="30">
+      <c r="C68" s="31">
         <v>480.33</v>
       </c>
-      <c r="D68" s="30">
+      <c r="D68" s="31">
         <v>102.31</v>
       </c>
-      <c r="E68" s="31"/>
-      <c r="F68" s="32">
+      <c r="E68" s="32"/>
+      <c r="F68" s="33">
         <v>4.49</v>
       </c>
-      <c r="G68" s="32">
+      <c r="G68" s="33">
         <v>9.61</v>
       </c>
-      <c r="H68" s="31"/>
-      <c r="I68" s="32">
+      <c r="H68" s="32"/>
+      <c r="I68" s="33">
         <v>17.72</v>
       </c>
-      <c r="J68" s="31"/>
-      <c r="K68" s="32">
+      <c r="J68" s="32"/>
+      <c r="K68" s="33">
         <v>20.59</v>
       </c>
-      <c r="L68" s="32">
+      <c r="L68" s="33">
         <v>5.31</v>
       </c>
-      <c r="M68" s="32">
+      <c r="M68" s="33">
         <v>5.63</v>
       </c>
-      <c r="N68" s="32">
+      <c r="N68" s="33">
         <v>7.33</v>
       </c>
-      <c r="O68" s="31"/>
-      <c r="P68" s="30">
+      <c r="O68" s="32"/>
+      <c r="P68" s="31">
         <v>1074.68</v>
       </c>
-      <c r="Q68" s="31"/>
-      <c r="R68" s="31"/>
-      <c r="S68" s="31"/>
-      <c r="T68" s="31"/>
-      <c r="U68" s="31"/>
-      <c r="V68" s="31"/>
-      <c r="W68" s="31"/>
-      <c r="X68" s="31"/>
-      <c r="Y68" s="31"/>
+      <c r="Q68" s="32"/>
+      <c r="R68" s="32"/>
+      <c r="S68" s="32"/>
+      <c r="T68" s="32"/>
+      <c r="U68" s="32"/>
+      <c r="V68" s="32"/>
+      <c r="W68" s="32"/>
+      <c r="X68" s="32"/>
+      <c r="Y68" s="32"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="29" t="s">
-        <v>488</v>
-      </c>
-      <c r="B69" s="32">
+      <c r="A69" s="30" t="s">
+        <v>489</v>
+      </c>
+      <c r="B69" s="33">
         <v>10.75</v>
       </c>
-      <c r="C69" s="32">
+      <c r="C69" s="33">
         <v>11.61</v>
       </c>
-      <c r="D69" s="32">
+      <c r="D69" s="33">
         <v>17.14</v>
       </c>
-      <c r="E69" s="32">
+      <c r="E69" s="33">
         <v>15.99</v>
       </c>
-      <c r="F69" s="32">
+      <c r="F69" s="33">
         <v>25.29</v>
       </c>
-      <c r="G69" s="32">
+      <c r="G69" s="33">
         <v>54.95</v>
       </c>
-      <c r="H69" s="32">
+      <c r="H69" s="33">
         <v>31.06</v>
       </c>
-      <c r="I69" s="32">
+      <c r="I69" s="33">
         <v>14.95</v>
       </c>
-      <c r="J69" s="32">
+      <c r="J69" s="33">
         <v>12.44</v>
       </c>
-      <c r="K69" s="32">
+      <c r="K69" s="33">
         <v>11.78</v>
       </c>
-      <c r="L69" s="32">
+      <c r="L69" s="33">
         <v>12.92</v>
       </c>
-      <c r="M69" s="32">
+      <c r="M69" s="33">
         <v>37.0</v>
       </c>
-      <c r="N69" s="31"/>
-      <c r="O69" s="31"/>
-      <c r="P69" s="31"/>
-      <c r="Q69" s="31"/>
-      <c r="R69" s="31"/>
-      <c r="S69" s="31"/>
-      <c r="T69" s="31"/>
-      <c r="U69" s="31"/>
-      <c r="V69" s="31"/>
-      <c r="W69" s="31"/>
-      <c r="X69" s="31"/>
-      <c r="Y69" s="31"/>
+      <c r="N69" s="32"/>
+      <c r="O69" s="32"/>
+      <c r="P69" s="32"/>
+      <c r="Q69" s="32"/>
+      <c r="R69" s="32"/>
+      <c r="S69" s="32"/>
+      <c r="T69" s="32"/>
+      <c r="U69" s="32"/>
+      <c r="V69" s="32"/>
+      <c r="W69" s="32"/>
+      <c r="X69" s="32"/>
+      <c r="Y69" s="32"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="27" t="s">
-        <v>489</v>
-      </c>
-      <c r="B70" s="28"/>
-      <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="28"/>
-      <c r="J70" s="28"/>
-      <c r="K70" s="28"/>
-      <c r="L70" s="28"/>
-      <c r="M70" s="28"/>
-      <c r="N70" s="28"/>
-      <c r="O70" s="28"/>
-      <c r="P70" s="28"/>
-      <c r="Q70" s="28"/>
-      <c r="R70" s="28"/>
-      <c r="S70" s="28"/>
-      <c r="T70" s="28"/>
-      <c r="U70" s="28"/>
-      <c r="V70" s="28"/>
-      <c r="W70" s="28"/>
-      <c r="X70" s="28"/>
-      <c r="Y70" s="28"/>
+      <c r="A70" s="28" t="s">
+        <v>490</v>
+      </c>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="29"/>
+      <c r="E70" s="29"/>
+      <c r="F70" s="29"/>
+      <c r="G70" s="29"/>
+      <c r="H70" s="29"/>
+      <c r="I70" s="29"/>
+      <c r="J70" s="29"/>
+      <c r="K70" s="29"/>
+      <c r="L70" s="29"/>
+      <c r="M70" s="29"/>
+      <c r="N70" s="29"/>
+      <c r="O70" s="29"/>
+      <c r="P70" s="29"/>
+      <c r="Q70" s="29"/>
+      <c r="R70" s="29"/>
+      <c r="S70" s="29"/>
+      <c r="T70" s="29"/>
+      <c r="U70" s="29"/>
+      <c r="V70" s="29"/>
+      <c r="W70" s="29"/>
+      <c r="X70" s="29"/>
+      <c r="Y70" s="29"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="29" t="s">
-        <v>490</v>
-      </c>
-      <c r="B71" s="32">
+      <c r="A71" s="30" t="s">
+        <v>491</v>
+      </c>
+      <c r="B71" s="33">
         <v>6.58</v>
       </c>
-      <c r="C71" s="31"/>
-      <c r="D71" s="31"/>
-      <c r="E71" s="31"/>
-      <c r="F71" s="32">
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="33">
         <v>4.58</v>
       </c>
-      <c r="G71" s="32">
+      <c r="G71" s="33">
         <v>9.79</v>
       </c>
-      <c r="H71" s="31"/>
-      <c r="I71" s="32">
+      <c r="H71" s="32"/>
+      <c r="I71" s="33">
         <v>22.41</v>
       </c>
-      <c r="J71" s="31"/>
-      <c r="K71" s="32">
+      <c r="J71" s="32"/>
+      <c r="K71" s="33">
         <v>25.57</v>
       </c>
-      <c r="L71" s="32">
+      <c r="L71" s="33">
         <v>5.59</v>
       </c>
-      <c r="M71" s="32">
+      <c r="M71" s="33">
         <v>5.92</v>
       </c>
-      <c r="N71" s="32">
+      <c r="N71" s="33">
         <v>7.71</v>
       </c>
-      <c r="O71" s="31"/>
-      <c r="P71" s="31"/>
-      <c r="Q71" s="31"/>
-      <c r="R71" s="31"/>
-      <c r="S71" s="31"/>
-      <c r="T71" s="31"/>
-      <c r="U71" s="31"/>
-      <c r="V71" s="31"/>
-      <c r="W71" s="31"/>
-      <c r="X71" s="31"/>
-      <c r="Y71" s="31"/>
+      <c r="O71" s="32"/>
+      <c r="P71" s="32"/>
+      <c r="Q71" s="32"/>
+      <c r="R71" s="32"/>
+      <c r="S71" s="32"/>
+      <c r="T71" s="32"/>
+      <c r="U71" s="32"/>
+      <c r="V71" s="32"/>
+      <c r="W71" s="32"/>
+      <c r="X71" s="32"/>
+      <c r="Y71" s="32"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="29" t="s">
-        <v>491</v>
-      </c>
-      <c r="B72" s="32">
+      <c r="A72" s="30" t="s">
+        <v>492</v>
+      </c>
+      <c r="B72" s="33">
         <v>13.04</v>
       </c>
-      <c r="C72" s="32">
+      <c r="C72" s="33">
         <v>12.83</v>
       </c>
-      <c r="D72" s="32">
+      <c r="D72" s="33">
         <v>19.13</v>
       </c>
-      <c r="E72" s="32">
+      <c r="E72" s="33">
         <v>17.76</v>
       </c>
-      <c r="F72" s="32">
+      <c r="F72" s="33">
         <v>29.48</v>
       </c>
-      <c r="G72" s="32">
+      <c r="G72" s="33">
         <v>87.01</v>
       </c>
-      <c r="H72" s="32">
+      <c r="H72" s="33">
         <v>41.46</v>
       </c>
-      <c r="I72" s="32">
+      <c r="I72" s="33">
         <v>17.3</v>
       </c>
-      <c r="J72" s="32">
+      <c r="J72" s="33">
         <v>13.86</v>
       </c>
-      <c r="K72" s="32">
+      <c r="K72" s="33">
         <v>13.1</v>
       </c>
-      <c r="L72" s="32">
+      <c r="L72" s="33">
         <v>14.43</v>
       </c>
-      <c r="M72" s="32">
+      <c r="M72" s="33">
         <v>49.31</v>
       </c>
-      <c r="N72" s="31"/>
-      <c r="O72" s="31"/>
-      <c r="P72" s="31"/>
-      <c r="Q72" s="31"/>
-      <c r="R72" s="31"/>
-      <c r="S72" s="31"/>
-      <c r="T72" s="31"/>
-      <c r="U72" s="31"/>
-      <c r="V72" s="31"/>
-      <c r="W72" s="31"/>
-      <c r="X72" s="31"/>
-      <c r="Y72" s="31"/>
+      <c r="N72" s="32"/>
+      <c r="O72" s="32"/>
+      <c r="P72" s="32"/>
+      <c r="Q72" s="32"/>
+      <c r="R72" s="32"/>
+      <c r="S72" s="32"/>
+      <c r="T72" s="32"/>
+      <c r="U72" s="32"/>
+      <c r="V72" s="32"/>
+      <c r="W72" s="32"/>
+      <c r="X72" s="32"/>
+      <c r="Y72" s="32"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
